--- a/irrbb_calc/output/eve_results.xlsx
+++ b/irrbb_calc/output/eve_results.xlsx
@@ -458,13 +458,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-6574540190.69358</v>
+        <v>-5829059488.05313</v>
       </c>
       <c r="D2" t="n">
-        <v>-183997797.7463385</v>
+        <v>-161752099.327705</v>
       </c>
       <c r="E2" t="n">
-        <v>-6758537988.439919</v>
+        <v>-5990811587.380835</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1753370960.005</v>
+        <v>1585760045.51</v>
       </c>
       <c r="D3" t="n">
-        <v>291778852.6655627</v>
+        <v>277236666.6892529</v>
       </c>
       <c r="E3" t="n">
-        <v>2045149812.670563</v>
+        <v>1862996712.199253</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +503,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-13681692.35639041</v>
+        <v>-22687228.01170084</v>
       </c>
       <c r="E4" t="n">
-        <v>-13681692.35639041</v>
+        <v>-22687228.01170084</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5222412409.557563</v>
+        <v>5215619182.619859</v>
       </c>
       <c r="D5" t="n">
-        <v>1701400411.943119</v>
+        <v>1702896520.096298</v>
       </c>
       <c r="E5" t="n">
-        <v>6923812821.500683</v>
+        <v>6918515702.716157</v>
       </c>
     </row>
   </sheetData>
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>401243178.8689833</v>
+        <v>972319740.0767289</v>
       </c>
       <c r="C2" t="n">
-        <v>1795499774.505953</v>
+        <v>1795693859.446145</v>
       </c>
       <c r="D2" t="n">
-        <v>2196742953.374937</v>
+        <v>2768013599.522874</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3036178985.198381</v>
+        <v>-2690905521.174497</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-3036178985.198381</v>
+        <v>-2690905521.174497</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-3036178985.198381</v>
+        <v>-2690905521.174497</v>
       </c>
     </row>
     <row r="3">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1824920590.468138</v>
+        <v>-1457759492.690205</v>
       </c>
       <c r="E3" t="n">
-        <v>-108443540.0901199</v>
+        <v>-86703986.71326756</v>
       </c>
       <c r="F3" t="n">
-        <v>-1933364130.558258</v>
+        <v>-1544463479.403473</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1933364130.558258</v>
+        <v>-1544463479.403473</v>
       </c>
     </row>
     <row r="4">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1446088354.574292</v>
+        <v>-1443444476.894019</v>
       </c>
       <c r="E4" t="n">
-        <v>-153911645.4257075</v>
+        <v>-101383518.964555</v>
       </c>
       <c r="F4" t="n">
-        <v>-1600000000</v>
+        <v>-1544827995.858574</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-1600000000</v>
+        <v>-1544827995.858574</v>
       </c>
     </row>
     <row r="5">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>732055192.5664563</v>
+        <v>1003305649.947738</v>
       </c>
       <c r="E5" t="n">
-        <v>143294884.4645993</v>
+        <v>189533485.9488289</v>
       </c>
       <c r="F5" t="n">
-        <v>875350077.0310557</v>
+        <v>1192839135.896567</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>875350077.0310557</v>
+        <v>1192839135.896567</v>
       </c>
     </row>
     <row r="6">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>919259602.1190236</v>
+        <v>494997876.2484202</v>
       </c>
       <c r="E6" t="n">
-        <v>158293266.495491</v>
+        <v>104255359.2445226</v>
       </c>
       <c r="F6" t="n">
-        <v>1077552868.614514</v>
+        <v>599253235.4929428</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1077552868.614514</v>
+        <v>599253235.4929428</v>
       </c>
     </row>
     <row r="7">
@@ -828,10 +828,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>168954272.6459035</v>
+        <v>225983456.3477748</v>
       </c>
       <c r="F7" t="n">
-        <v>168954272.6459035</v>
+        <v>225983456.3477748</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>168954272.6459035</v>
+        <v>225983456.3477748</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-218136855.2933449</v>
+        <v>-298037660.7261487</v>
       </c>
       <c r="F8" t="n">
-        <v>-218136855.2933449</v>
+        <v>-298037660.7261487</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-218136855.2933449</v>
+        <v>-298037660.7261487</v>
       </c>
     </row>
     <row r="9">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1602369803.595113</v>
+        <v>1760739231.272845</v>
       </c>
       <c r="E9" t="n">
-        <v>512274903.9197781</v>
+        <v>543648252.9612641</v>
       </c>
       <c r="F9" t="n">
-        <v>2114644707.514891</v>
+        <v>2304387484.234109</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2114644707.514891</v>
+        <v>2304387484.234109</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3245441231.836967</v>
+        <v>3085125471.493792</v>
       </c>
       <c r="E10" t="n">
-        <v>907841824.286764</v>
+        <v>1340509063.916663</v>
       </c>
       <c r="F10" t="n">
-        <v>4153283056.123731</v>
+        <v>4425634535.410456</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4153283056.123731</v>
+        <v>4425634535.410456</v>
       </c>
     </row>
     <row r="11">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3384461943.872222</v>
+        <v>-2998690450.401045</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-3384461943.872222</v>
+        <v>-2998690450.401045</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3384461943.872222</v>
+        <v>-2998690450.401045</v>
       </c>
     </row>
     <row r="12">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1936207299.14906</v>
+        <v>-1546608872.763171</v>
       </c>
       <c r="E12" t="n">
-        <v>-112494774.1408907</v>
+        <v>-89941174.82012209</v>
       </c>
       <c r="F12" t="n">
-        <v>-2048702073.289951</v>
+        <v>-1636550047.583293</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-2048702073.289951</v>
+        <v>-1636550047.583293</v>
       </c>
     </row>
     <row r="13">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1543476032.970207</v>
+        <v>-1540499630.658895</v>
       </c>
       <c r="E13" t="n">
-        <v>-57449575.39913751</v>
+        <v>-43918813.40473859</v>
       </c>
       <c r="F13" t="n">
-        <v>-1600925608.369344</v>
+        <v>-1584418444.063634</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-1600925608.369344</v>
+        <v>-1584418444.063634</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>831131954.9521571</v>
+        <v>1123670524.367797</v>
       </c>
       <c r="E14" t="n">
-        <v>157594951.5775557</v>
+        <v>205901206.9691528</v>
       </c>
       <c r="F14" t="n">
-        <v>988726906.5297129</v>
+        <v>1329571731.33695</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>988726906.5297129</v>
+        <v>1329571731.33695</v>
       </c>
     </row>
     <row r="15">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1033082706.164304</v>
+        <v>556096841.5974141</v>
       </c>
       <c r="E15" t="n">
-        <v>58719632.9625892</v>
+        <v>53745204.18767112</v>
       </c>
       <c r="F15" t="n">
-        <v>1091802339.126893</v>
+        <v>609842045.7850852</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1091802339.126893</v>
+        <v>609842045.7850852</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>181750152.0315814</v>
+        <v>242089636.7602372</v>
       </c>
       <c r="F16" t="n">
-        <v>181750152.0315814</v>
+        <v>242089636.7602372</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>181750152.0315814</v>
+        <v>242089636.7602372</v>
       </c>
     </row>
     <row r="17">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-79190556.51509377</v>
+        <v>-112037162.7717351</v>
       </c>
       <c r="F17" t="n">
-        <v>-79190556.51509377</v>
+        <v>-112037162.7717351</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-79190556.51509377</v>
+        <v>-112037162.7717351</v>
       </c>
     </row>
     <row r="18">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1831073515.712449</v>
+        <v>2007946824.812527</v>
       </c>
       <c r="E18" t="n">
-        <v>565756718.6347049</v>
+        <v>599813304.7980036</v>
       </c>
       <c r="F18" t="n">
-        <v>2396830234.347154</v>
+        <v>2607760129.610531</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2396830234.347154</v>
+        <v>2607760129.610531</v>
       </c>
     </row>
     <row r="19">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3811519265.426297</v>
+        <v>3622006681.784953</v>
       </c>
       <c r="E19" t="n">
-        <v>355607645.8375233</v>
+        <v>895998235.616595</v>
       </c>
       <c r="F19" t="n">
-        <v>4167126911.263821</v>
+        <v>4518004917.401548</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4167126911.263821</v>
+        <v>4518004917.401548</v>
       </c>
     </row>
     <row r="20">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3125222363.821362</v>
+        <v>-2769645556.163737</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-3125222363.821362</v>
+        <v>-2769645556.163737</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-3125222363.821362</v>
+        <v>-2769645556.163737</v>
       </c>
     </row>
     <row r="21">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1871762993.456914</v>
+        <v>-1495167285.930043</v>
       </c>
       <c r="E21" t="n">
-        <v>-110503220.1985472</v>
+        <v>-88350239.98202153</v>
       </c>
       <c r="F21" t="n">
-        <v>-1982266213.655461</v>
+        <v>-1583517525.912064</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-1982266213.655461</v>
+        <v>-1583517525.912064</v>
       </c>
     </row>
     <row r="22">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1478375551.697844</v>
+        <v>-1475636526.909071</v>
       </c>
       <c r="E22" t="n">
-        <v>-121624448.3021563</v>
+        <v>-82517849.24404341</v>
       </c>
       <c r="F22" t="n">
-        <v>-1600000000</v>
+        <v>-1558154376.153114</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>-1600000000</v>
+        <v>-1558154376.153114</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>759141232.3516999</v>
+        <v>1037530254.908582</v>
       </c>
       <c r="E23" t="n">
-        <v>147654781.2767044</v>
+        <v>194817450.937475</v>
       </c>
       <c r="F23" t="n">
-        <v>906796013.6284044</v>
+        <v>1232347705.846057</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>906796013.6284044</v>
+        <v>1232347705.846057</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>951375292.5956407</v>
+        <v>512826939.5976719</v>
       </c>
       <c r="E24" t="n">
-        <v>136529372.6919434</v>
+        <v>93942183.66001469</v>
       </c>
       <c r="F24" t="n">
-        <v>1087904665.287584</v>
+        <v>606769123.2576867</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1087904665.287584</v>
+        <v>606769123.2576867</v>
       </c>
     </row>
     <row r="25">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>173500457.7166572</v>
+        <v>231951716.8009863</v>
       </c>
       <c r="F25" t="n">
-        <v>173500457.7166572</v>
+        <v>231951716.8009863</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>173500457.7166572</v>
+        <v>231951716.8009863</v>
       </c>
     </row>
     <row r="26">
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-184352638.8556274</v>
+        <v>-250602138.3130837</v>
       </c>
       <c r="F26" t="n">
-        <v>-184352638.8556274</v>
+        <v>-250602138.3130837</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-184352638.8556274</v>
+        <v>-250602138.3130837</v>
       </c>
     </row>
     <row r="27">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1662470601.88792</v>
+        <v>1826106748.523909</v>
       </c>
       <c r="E27" t="n">
-        <v>528160164.6008554</v>
+        <v>560400874.1863053</v>
       </c>
       <c r="F27" t="n">
-        <v>2190630766.488776</v>
+        <v>2386507622.710215</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2190630766.488776</v>
+        <v>2386507622.710215</v>
       </c>
     </row>
     <row r="28">
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3384708277.030074</v>
+        <v>3217279872.432061</v>
       </c>
       <c r="E28" t="n">
-        <v>776093949.1430231</v>
+        <v>1255980480.195157</v>
       </c>
       <c r="F28" t="n">
-        <v>4160802226.173097</v>
+        <v>4473260352.627217</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4160802226.173097</v>
+        <v>4473260352.627217</v>
       </c>
     </row>
     <row r="29">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-3264694037.168396</v>
+        <v>-2892803078.898238</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-3264694037.168396</v>
+        <v>-2892803078.898238</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-3264694037.168396</v>
+        <v>-2892803078.898238</v>
       </c>
     </row>
     <row r="30">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1880679900.593472</v>
+        <v>-1502266857.173224</v>
       </c>
       <c r="E30" t="n">
-        <v>-110107388.7090437</v>
+        <v>-88033049.57662189</v>
       </c>
       <c r="F30" t="n">
-        <v>-1990787289.302516</v>
+        <v>-1590299906.749846</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-1990787289.302516</v>
+        <v>-1590299906.749846</v>
       </c>
     </row>
     <row r="31">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-1503570480.906211</v>
+        <v>-1500715085.193099</v>
       </c>
       <c r="E31" t="n">
-        <v>-96429519.09378876</v>
+        <v>-67272919.76085947</v>
       </c>
       <c r="F31" t="n">
-        <v>-1600000000</v>
+        <v>-1567988004.953959</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1600000000</v>
+        <v>-1567988004.953959</v>
       </c>
     </row>
     <row r="32">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>795606744.653574</v>
+        <v>1079449621.754515</v>
       </c>
       <c r="E32" t="n">
-        <v>152066120.8258412</v>
+        <v>199292876.9890093</v>
       </c>
       <c r="F32" t="n">
-        <v>947672865.4794152</v>
+        <v>1278742498.743524</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>947672865.4794152</v>
+        <v>1278742498.743524</v>
       </c>
     </row>
     <row r="33">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>991682689.84187</v>
+        <v>533643017.0907862</v>
       </c>
       <c r="E33" t="n">
-        <v>88489164.67520773</v>
+        <v>67739350.30410285</v>
       </c>
       <c r="F33" t="n">
-        <v>1080171854.517078</v>
+        <v>601382367.394889</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1080171854.517078</v>
+        <v>601382367.394889</v>
       </c>
     </row>
     <row r="34">
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>176203412.824702</v>
+        <v>234863905.2277696</v>
       </c>
       <c r="F34" t="n">
-        <v>176203412.824702</v>
+        <v>234863905.2277696</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>176203412.824702</v>
+        <v>234863905.2277696</v>
       </c>
     </row>
     <row r="35">
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-123577861.1196219</v>
+        <v>-173508641.9408788</v>
       </c>
       <c r="F35" t="n">
-        <v>-123577861.1196219</v>
+        <v>-173508641.9408788</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-123577861.1196219</v>
+        <v>-173508641.9408788</v>
       </c>
     </row>
     <row r="36">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1750864697.728256</v>
+        <v>1920903864.190894</v>
       </c>
       <c r="E36" t="n">
-        <v>545406184.9158299</v>
+        <v>578375801.3371502</v>
       </c>
       <c r="F36" t="n">
-        <v>2296270882.644086</v>
+        <v>2499279665.528044</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2296270882.644086</v>
+        <v>2499279665.528044</v>
       </c>
     </row>
     <row r="37">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3618451091.859318</v>
+        <v>3438827012.264998</v>
       </c>
       <c r="E37" t="n">
-        <v>538062458.5979781</v>
+        <v>1022223397.274345</v>
       </c>
       <c r="F37" t="n">
-        <v>4156513550.457296</v>
+        <v>4461050409.539343</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4156513550.457296</v>
+        <v>4461050409.539343</v>
       </c>
     </row>
     <row r="38">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-3186773502.101998</v>
+        <v>-2823950121.560254</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-3186773502.101998</v>
+        <v>-2823950121.560254</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-3186773502.101998</v>
+        <v>-2823950121.560254</v>
       </c>
     </row>
     <row r="39">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1858334436.141835</v>
+        <v>-1484427782.146688</v>
       </c>
       <c r="E39" t="n">
-        <v>-109335941.330991</v>
+        <v>-87416666.97081165</v>
       </c>
       <c r="F39" t="n">
-        <v>-1967670377.472826</v>
+        <v>-1571844449.1175</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-1967670377.472826</v>
+        <v>-1571844449.1175</v>
       </c>
     </row>
     <row r="40">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1482873031.853683</v>
+        <v>-1480090213.710917</v>
       </c>
       <c r="E40" t="n">
-        <v>-117126968.1463175</v>
+        <v>-79507650.93301579</v>
       </c>
       <c r="F40" t="n">
-        <v>-1600000000</v>
+        <v>-1559597864.643933</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>-1600000000</v>
+        <v>-1559597864.643933</v>
       </c>
     </row>
     <row r="41">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>773696056.7490882</v>
+        <v>1053041223.126753</v>
       </c>
       <c r="E41" t="n">
-        <v>148969112.3128394</v>
+        <v>195788025.1981952</v>
       </c>
       <c r="F41" t="n">
-        <v>922665169.0619277</v>
+        <v>1248829248.324949</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>922665169.0619277</v>
+        <v>1248829248.324949</v>
       </c>
     </row>
     <row r="42">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>966689197.0551194</v>
+        <v>520369633.7373804</v>
       </c>
       <c r="E42" t="n">
-        <v>111126422.2322921</v>
+        <v>79240918.93445104</v>
       </c>
       <c r="F42" t="n">
-        <v>1077815619.287411</v>
+        <v>599610552.6718315</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1077815619.287411</v>
+        <v>599610552.6718315</v>
       </c>
     </row>
     <row r="43">
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>173523294.9651389</v>
+        <v>231523105.7736381</v>
       </c>
       <c r="F43" t="n">
-        <v>173523294.9651389</v>
+        <v>231523105.7736381</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>173523294.9651389</v>
+        <v>231523105.7736381</v>
       </c>
     </row>
     <row r="44">
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-154616086.4940273</v>
+        <v>-214715593.5455545</v>
       </c>
       <c r="F44" t="n">
-        <v>-154616086.4940273</v>
+        <v>-214715593.5455545</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-154616086.4940273</v>
+        <v>-214715593.5455545</v>
       </c>
     </row>
     <row r="45">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1699935419.936986</v>
+        <v>1865913055.941358</v>
       </c>
       <c r="E45" t="n">
-        <v>533759833.4001645</v>
+        <v>566154791.9938717</v>
       </c>
       <c r="F45" t="n">
-        <v>2233695253.337151</v>
+        <v>2432067847.93523</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2233695253.337151</v>
+        <v>2432067847.93523</v>
       </c>
     </row>
     <row r="46">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3490848074.78879</v>
+        <v>3317816108.356492</v>
       </c>
       <c r="E46" t="n">
-        <v>663505807.0666398</v>
+        <v>1125443036.759046</v>
       </c>
       <c r="F46" t="n">
-        <v>4154353881.85543</v>
+        <v>4443259145.115538</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4154353881.85543</v>
+        <v>4443259145.115538</v>
       </c>
     </row>
     <row r="47">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3216377295.898001</v>
+        <v>-2850201929.012933</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-3216377295.898001</v>
+        <v>-2850201929.012933</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-3216377295.898001</v>
+        <v>-2850201929.012933</v>
       </c>
     </row>
     <row r="48">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1901104479.556713</v>
+        <v>-1518592791.667027</v>
       </c>
       <c r="E48" t="n">
-        <v>-111562068.6546139</v>
+        <v>-89196313.61769548</v>
       </c>
       <c r="F48" t="n">
-        <v>-2012666548.211327</v>
+        <v>-1607789105.284723</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>-2012666548.211327</v>
+        <v>-1607789105.284723</v>
       </c>
     </row>
     <row r="49">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1504104393.813034</v>
+        <v>-1501277315.229708</v>
       </c>
       <c r="E49" t="n">
-        <v>-95895606.18696575</v>
+        <v>-67331143.89183764</v>
       </c>
       <c r="F49" t="n">
-        <v>-1600000000</v>
+        <v>-1568608459.121546</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1600000000</v>
+        <v>-1568608459.121546</v>
       </c>
     </row>
     <row r="50">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>785137458.9800514</v>
+        <v>1069184728.843646</v>
       </c>
       <c r="E50" t="n">
-        <v>151418618.7033986</v>
+        <v>199127253.849196</v>
       </c>
       <c r="F50" t="n">
-        <v>936556077.6834501</v>
+        <v>1268311982.692842</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>936556077.6834501</v>
+        <v>1268311982.692842</v>
       </c>
     </row>
     <row r="51">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>981351177.4107454</v>
+        <v>529042882.7316132</v>
       </c>
       <c r="E51" t="n">
-        <v>110179039.6696923</v>
+        <v>80425193.85123558</v>
       </c>
       <c r="F51" t="n">
-        <v>1091530217.080438</v>
+        <v>609468076.5828488</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1091530217.080438</v>
+        <v>609468076.5828488</v>
       </c>
     </row>
     <row r="52">
@@ -2358,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>176878488.7514104</v>
+        <v>236202807.0962931</v>
       </c>
       <c r="F52" t="n">
-        <v>176878488.7514104</v>
+        <v>236202807.0962931</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>176878488.7514104</v>
+        <v>236202807.0962931</v>
       </c>
     </row>
     <row r="53">
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>-147403220.6232742</v>
+        <v>-201069936.43319</v>
       </c>
       <c r="F53" t="n">
-        <v>-147403220.6232742</v>
+        <v>-201069936.43319</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-147403220.6232742</v>
+        <v>-201069936.43319</v>
       </c>
     </row>
     <row r="54">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1722353777.195394</v>
+        <v>1890848440.179662</v>
       </c>
       <c r="E54" t="n">
-        <v>542215165.8800309</v>
+        <v>575161723.7373053</v>
       </c>
       <c r="F54" t="n">
-        <v>2264568943.075425</v>
+        <v>2466010163.916968</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2264568943.075425</v>
+        <v>2466010163.916968</v>
       </c>
     </row>
     <row r="55">
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3531985352.731571</v>
+        <v>3356961299.75534</v>
       </c>
       <c r="E55" t="n">
-        <v>631829240.4980906</v>
+        <v>1139828758.864909</v>
       </c>
       <c r="F55" t="n">
-        <v>4163814593.229662</v>
+        <v>4496790058.620248</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4163814593.229662</v>
+        <v>4496790058.620248</v>
       </c>
     </row>
     <row r="56">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-3272460509.809211</v>
+        <v>-2899717606.748238</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-3272460509.809211</v>
+        <v>-2899717606.748238</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>-3272460509.809211</v>
+        <v>-2899717606.748238</v>
       </c>
     </row>
     <row r="57">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1902003141.24399</v>
+        <v>-1519301097.610961</v>
       </c>
       <c r="E57" t="n">
-        <v>-111257233.8668509</v>
+        <v>-88952311.92939194</v>
       </c>
       <c r="F57" t="n">
-        <v>-2013260375.110841</v>
+        <v>-1608253409.540353</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>-2013260375.110841</v>
+        <v>-1608253409.540353</v>
       </c>
     </row>
     <row r="58">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1513119392.725879</v>
+        <v>-1510247230.276803</v>
       </c>
       <c r="E58" t="n">
-        <v>-86880607.27412109</v>
+        <v>-61835301.53727505</v>
       </c>
       <c r="F58" t="n">
-        <v>-1600000000</v>
+        <v>-1572082531.814079</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>-1600000000</v>
+        <v>-1572082531.814079</v>
       </c>
     </row>
     <row r="59">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>799530453.2467377</v>
+        <v>1085507522.92363</v>
       </c>
       <c r="E59" t="n">
-        <v>153086314.7247133</v>
+        <v>200763212.83173</v>
       </c>
       <c r="F59" t="n">
-        <v>952616767.971451</v>
+        <v>1286270735.75536</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>952616767.971451</v>
+        <v>1286270735.75536</v>
       </c>
     </row>
     <row r="60">
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>997076898.4113147</v>
+        <v>537038850.6102486</v>
       </c>
       <c r="E60" t="n">
-        <v>90421940.54264526</v>
+        <v>69601404.42702724</v>
       </c>
       <c r="F60" t="n">
-        <v>1087498838.95396</v>
+        <v>606640255.0372758</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1087498838.95396</v>
+        <v>606640255.0372758</v>
       </c>
     </row>
     <row r="61">
@@ -2664,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>177775828.0781509</v>
+        <v>237100266.3066151</v>
       </c>
       <c r="F61" t="n">
-        <v>177775828.0781509</v>
+        <v>237100266.3066151</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>177775828.0781509</v>
+        <v>237100266.3066151</v>
       </c>
     </row>
     <row r="62">
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-122887238.6856817</v>
+        <v>-170297515.8426302</v>
       </c>
       <c r="F62" t="n">
-        <v>-122887238.6856817</v>
+        <v>-170297515.8426302</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>-122887238.6856817</v>
+        <v>-170297515.8426302</v>
       </c>
     </row>
     <row r="63">
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1757658381.030332</v>
+        <v>1928647122.516229</v>
       </c>
       <c r="E63" t="n">
-        <v>548819220.321909</v>
+        <v>582032069.7271385</v>
       </c>
       <c r="F63" t="n">
-        <v>2306477601.352241</v>
+        <v>2510679192.243367</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2306477601.352241</v>
+        <v>2510679192.243367</v>
       </c>
     </row>
     <row r="64">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3626994159.495385</v>
+        <v>3447003500.187933</v>
       </c>
       <c r="E64" t="n">
-        <v>534514959.676621</v>
+        <v>1041635687.089756</v>
       </c>
       <c r="F64" t="n">
-        <v>4161509119.172007</v>
+        <v>4488639187.277689</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4161509119.172007</v>
+        <v>4488639187.277689</v>
       </c>
     </row>
   </sheetData>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>191937899.8767481</v>
+        <v>752058738.2040737</v>
       </c>
       <c r="C2" t="n">
-        <v>1410167111.003364</v>
+        <v>1917804452.015082</v>
       </c>
       <c r="D2" t="n">
-        <v>1602105010.880112</v>
+        <v>2669863190.219156</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-594637942.4948254</v>
+        <v>-98150409.30371809</v>
       </c>
       <c r="G2" t="n">
-        <v>-49.55316187456878</v>
+        <v>-5.452800516873228</v>
       </c>
       <c r="H2" t="n">
-        <v>-594637942.4948254</v>
+        <v>-98150409.30371809</v>
       </c>
       <c r="I2" t="n">
-        <v>-49.55316187456878</v>
+        <v>-5.452800516873228</v>
       </c>
     </row>
     <row r="3">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>642662166.2637186</v>
+        <v>1223921918.739581</v>
       </c>
       <c r="C3" t="n">
-        <v>1070294194.988833</v>
+        <v>1751650437.335064</v>
       </c>
       <c r="D3" t="n">
-        <v>1712956361.252552</v>
+        <v>2975572356.074646</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-483786592.122385</v>
+        <v>207558756.5517716</v>
       </c>
       <c r="G3" t="n">
-        <v>-40.31554934353208</v>
+        <v>11.53104203065398</v>
       </c>
       <c r="H3" t="n">
-        <v>-483786592.122385</v>
+        <v>103779378.2758858</v>
       </c>
       <c r="I3" t="n">
-        <v>-40.31554934353208</v>
+        <v>5.76552101532699</v>
       </c>
     </row>
     <row r="4">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>282334494.8892155</v>
+        <v>853294446.459373</v>
       </c>
       <c r="C4" t="n">
-        <v>1345458418.072853</v>
+        <v>1915622478.240789</v>
       </c>
       <c r="D4" t="n">
-        <v>1627792912.962068</v>
+        <v>2768916924.700162</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-568950040.412869</v>
+        <v>903325.1772880554</v>
       </c>
       <c r="G4" t="n">
-        <v>-47.41250336773908</v>
+        <v>0.05018473207155864</v>
       </c>
       <c r="H4" t="n">
-        <v>-568950040.412869</v>
+        <v>451662.5886440277</v>
       </c>
       <c r="I4" t="n">
-        <v>-47.41250336773908</v>
+        <v>0.02509236603577932</v>
       </c>
     </row>
     <row r="5">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>507660805.4149399</v>
+        <v>1077038494.036631</v>
       </c>
       <c r="C5" t="n">
-        <v>1170112572.917104</v>
+        <v>1773680719.854016</v>
       </c>
       <c r="D5" t="n">
-        <v>1677773378.332044</v>
+        <v>2850719213.890648</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-518969575.0428934</v>
+        <v>82705614.36777401</v>
       </c>
       <c r="G5" t="n">
-        <v>-43.24746458690779</v>
+        <v>4.594756353765223</v>
       </c>
       <c r="H5" t="n">
-        <v>-518969575.0428934</v>
+        <v>41352807.183887</v>
       </c>
       <c r="I5" t="n">
-        <v>-43.24746458690779</v>
+        <v>2.297378176882611</v>
       </c>
     </row>
     <row r="6">
@@ -2980,13 +2980,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>403187778.4324675</v>
+        <v>968671903.7441241</v>
       </c>
       <c r="C6" t="n">
-        <v>1249805474.005739</v>
+        <v>1816509967.20982</v>
       </c>
       <c r="D6" t="n">
-        <v>1652993252.438207</v>
+        <v>2785181870.953945</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-543749700.9367304</v>
+        <v>17168271.4310708</v>
       </c>
       <c r="G6" t="n">
-        <v>-45.31247507806086</v>
+        <v>0.9537928572817114</v>
       </c>
       <c r="H6" t="n">
-        <v>-543749700.9367304</v>
+        <v>8584135.715535402</v>
       </c>
       <c r="I6" t="n">
-        <v>-45.31247507806086</v>
+        <v>0.4768964286408557</v>
       </c>
     </row>
     <row r="7">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>399241597.050014</v>
+        <v>975965315.6005923</v>
       </c>
       <c r="C7" t="n">
-        <v>1257659658.037769</v>
+        <v>1873148343.456216</v>
       </c>
       <c r="D7" t="n">
-        <v>1656901255.087783</v>
+        <v>2849113659.056808</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3027,16 +3027,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-539841698.2871537</v>
+        <v>81100059.53393412</v>
       </c>
       <c r="G7" t="n">
-        <v>-44.98680819059614</v>
+        <v>4.50555886299634</v>
       </c>
       <c r="H7" t="n">
-        <v>-539841698.2871537</v>
+        <v>40550029.76696706</v>
       </c>
       <c r="I7" t="n">
-        <v>-44.98680819059614</v>
+        <v>2.25277943149817</v>
       </c>
     </row>
     <row r="8">
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>493676848.4046888</v>
+        <v>1068931061.602039</v>
       </c>
       <c r="C8" t="n">
-        <v>1183593183.517386</v>
+        <v>1810047511.07297</v>
       </c>
       <c r="D8" t="n">
-        <v>1677270031.922075</v>
+        <v>2878978572.675008</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-519472921.4528623</v>
+        <v>110964973.1521344</v>
       </c>
       <c r="G8" t="n">
-        <v>-43.28941012107185</v>
+        <v>6.164720730674135</v>
       </c>
       <c r="H8" t="n">
-        <v>-519472921.4528623</v>
+        <v>55482486.57606721</v>
       </c>
       <c r="I8" t="n">
-        <v>-43.28941012107185</v>
+        <v>3.082360365337067</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/eve_results.xlsx
+++ b/irrbb_calc/output/eve_results.xlsx
@@ -458,13 +458,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-5829059488.05313</v>
+        <v>-5837029699.068525</v>
       </c>
       <c r="D2" t="n">
-        <v>-161752099.327705</v>
+        <v>-161844533.8616113</v>
       </c>
       <c r="E2" t="n">
-        <v>-5990811587.380835</v>
+        <v>-5998874232.930137</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1585760045.51</v>
+        <v>1278847057.85</v>
       </c>
       <c r="D3" t="n">
-        <v>277236666.6892529</v>
+        <v>231584150.3581635</v>
       </c>
       <c r="E3" t="n">
-        <v>1862996712.199253</v>
+        <v>1510431208.208163</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +503,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-22687228.01170084</v>
+        <v>-14336961.1800304</v>
       </c>
       <c r="E4" t="n">
-        <v>-22687228.01170084</v>
+        <v>-14336961.1800304</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5215619182.619859</v>
+        <v>5233457764.944227</v>
       </c>
       <c r="D5" t="n">
-        <v>1702896520.096298</v>
+        <v>1693640251.583912</v>
       </c>
       <c r="E5" t="n">
-        <v>6918515702.716157</v>
+        <v>6927098016.528139</v>
       </c>
     </row>
   </sheetData>
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>972319740.0767289</v>
+        <v>675275123.7257019</v>
       </c>
       <c r="C2" t="n">
-        <v>1795693859.446145</v>
+        <v>1749042906.900434</v>
       </c>
       <c r="D2" t="n">
-        <v>2768013599.522874</v>
+        <v>2424318030.626136</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2690905521.174497</v>
+        <v>-2695465919.310573</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-2690905521.174497</v>
+        <v>-2695465919.310573</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2690905521.174497</v>
+        <v>-2695465919.310573</v>
       </c>
     </row>
     <row r="3">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1457759492.690205</v>
+        <v>-1459014759.962479</v>
       </c>
       <c r="E3" t="n">
-        <v>-86703986.71326756</v>
+        <v>-86735165.71982653</v>
       </c>
       <c r="F3" t="n">
-        <v>-1544463479.403473</v>
+        <v>-1545749925.682306</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1544463479.403473</v>
+        <v>-1545749925.682306</v>
       </c>
     </row>
     <row r="4">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1443444476.894019</v>
+        <v>-1444967479.344626</v>
       </c>
       <c r="E4" t="n">
-        <v>-101383518.964555</v>
+        <v>-101462878.7715522</v>
       </c>
       <c r="F4" t="n">
-        <v>-1544827995.858574</v>
+        <v>-1546430358.116178</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-1544827995.858574</v>
+        <v>-1546430358.116178</v>
       </c>
     </row>
     <row r="5">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1003305649.947738</v>
+        <v>884354622.0529087</v>
       </c>
       <c r="E5" t="n">
-        <v>189533485.9488289</v>
+        <v>181942076.7411945</v>
       </c>
       <c r="F5" t="n">
-        <v>1192839135.896567</v>
+        <v>1066296698.794103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1192839135.896567</v>
+        <v>1066296698.794103</v>
       </c>
     </row>
     <row r="6">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>494997876.2484202</v>
+        <v>317529440.6810989</v>
       </c>
       <c r="E6" t="n">
-        <v>104255359.2445226</v>
+        <v>51020927.52694491</v>
       </c>
       <c r="F6" t="n">
-        <v>599253235.4929428</v>
+        <v>368550368.2080438</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>599253235.4929428</v>
+        <v>368550368.2080438</v>
       </c>
     </row>
     <row r="7">
@@ -828,10 +828,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>225983456.3477748</v>
+        <v>189032198.9218521</v>
       </c>
       <c r="F7" t="n">
-        <v>225983456.3477748</v>
+        <v>189032198.9218521</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>225983456.3477748</v>
+        <v>189032198.9218521</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-298037660.7261487</v>
+        <v>-284716169.7502007</v>
       </c>
       <c r="F8" t="n">
-        <v>-298037660.7261487</v>
+        <v>-284716169.7502007</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-298037660.7261487</v>
+        <v>-284716169.7502007</v>
       </c>
     </row>
     <row r="9">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1760739231.272845</v>
+        <v>1764517613.794478</v>
       </c>
       <c r="E9" t="n">
-        <v>543648252.9612641</v>
+        <v>545265787.1551471</v>
       </c>
       <c r="F9" t="n">
-        <v>2304387484.234109</v>
+        <v>2309783400.949625</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2304387484.234109</v>
+        <v>2309783400.949625</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3085125471.493792</v>
+        <v>3098391674.511272</v>
       </c>
       <c r="E10" t="n">
-        <v>1340509063.916663</v>
+        <v>1329884892.779564</v>
       </c>
       <c r="F10" t="n">
-        <v>4425634535.410456</v>
+        <v>4428276567.290836</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4425634535.410456</v>
+        <v>4428276567.290836</v>
       </c>
     </row>
     <row r="11">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2998690450.401045</v>
+        <v>-3004287080.358242</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-2998690450.401045</v>
+        <v>-3004287080.358242</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-2998690450.401045</v>
+        <v>-3004287080.358242</v>
       </c>
     </row>
     <row r="12">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1546608872.763171</v>
+        <v>-1547967289.521232</v>
       </c>
       <c r="E12" t="n">
-        <v>-89941174.82012209</v>
+        <v>-89974597.74089299</v>
       </c>
       <c r="F12" t="n">
-        <v>-1636550047.583293</v>
+        <v>-1637941887.262125</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-1636550047.583293</v>
+        <v>-1637941887.262125</v>
       </c>
     </row>
     <row r="13">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1540499630.658895</v>
+        <v>-1542214172.839975</v>
       </c>
       <c r="E13" t="n">
-        <v>-43918813.40473859</v>
+        <v>-44136590.95281409</v>
       </c>
       <c r="F13" t="n">
-        <v>-1584418444.063634</v>
+        <v>-1586350763.792789</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-1584418444.063634</v>
+        <v>-1586350763.792789</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1123670524.367797</v>
+        <v>1016494720.626164</v>
       </c>
       <c r="E14" t="n">
-        <v>205901206.9691528</v>
+        <v>200633258.7332544</v>
       </c>
       <c r="F14" t="n">
-        <v>1329571731.33695</v>
+        <v>1217127979.359418</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1329571731.33695</v>
+        <v>1217127979.359418</v>
       </c>
     </row>
     <row r="15">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>556096841.5974141</v>
+        <v>345848757.3690892</v>
       </c>
       <c r="E15" t="n">
-        <v>53745204.18767112</v>
+        <v>29333222.07038736</v>
       </c>
       <c r="F15" t="n">
-        <v>609842045.7850852</v>
+        <v>375181979.4394766</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>609842045.7850852</v>
+        <v>375181979.4394766</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>242089636.7602372</v>
+        <v>202242745.6677688</v>
       </c>
       <c r="F16" t="n">
-        <v>242089636.7602372</v>
+        <v>202242745.6677688</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>242089636.7602372</v>
+        <v>202242745.6677688</v>
       </c>
     </row>
     <row r="17">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-112037162.7717351</v>
+        <v>-130116086.0134829</v>
       </c>
       <c r="F17" t="n">
-        <v>-112037162.7717351</v>
+        <v>-130116086.0134829</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-112037162.7717351</v>
+        <v>-130116086.0134829</v>
       </c>
     </row>
     <row r="18">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2007946824.812527</v>
+        <v>2012072973.872798</v>
       </c>
       <c r="E18" t="n">
-        <v>599813304.7980036</v>
+        <v>601658611.9384332</v>
       </c>
       <c r="F18" t="n">
-        <v>2607760129.610531</v>
+        <v>2613731585.811231</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2607760129.610531</v>
+        <v>2613731585.811231</v>
       </c>
     </row>
     <row r="19">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3622006681.784953</v>
+        <v>3636496095.83037</v>
       </c>
       <c r="E19" t="n">
-        <v>895998235.616595</v>
+        <v>884850195.0321769</v>
       </c>
       <c r="F19" t="n">
-        <v>4518004917.401548</v>
+        <v>4521346290.862547</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4518004917.401548</v>
+        <v>4521346290.862547</v>
       </c>
     </row>
     <row r="20">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-2769645556.163737</v>
+        <v>-2774441796.51401</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-2769645556.163737</v>
+        <v>-2774441796.51401</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-2769645556.163737</v>
+        <v>-2774441796.51401</v>
       </c>
     </row>
     <row r="21">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1495167285.930043</v>
+        <v>-1496460323.905028</v>
       </c>
       <c r="E21" t="n">
-        <v>-88350239.98202153</v>
+        <v>-88382304.60151681</v>
       </c>
       <c r="F21" t="n">
-        <v>-1583517525.912064</v>
+        <v>-1584842628.506545</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-1583517525.912064</v>
+        <v>-1584842628.506545</v>
       </c>
     </row>
     <row r="22">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1475636526.909071</v>
+        <v>-1477214337.526204</v>
       </c>
       <c r="E22" t="n">
-        <v>-82517849.24404341</v>
+        <v>-82593056.79185569</v>
       </c>
       <c r="F22" t="n">
-        <v>-1558154376.153114</v>
+        <v>-1559807394.31806</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>-1558154376.153114</v>
+        <v>-1559807394.31806</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1037530254.908582</v>
+        <v>919157170.8797625</v>
       </c>
       <c r="E23" t="n">
-        <v>194817450.937475</v>
+        <v>187716428.0752255</v>
       </c>
       <c r="F23" t="n">
-        <v>1232347705.846057</v>
+        <v>1106873598.954988</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1232347705.846057</v>
+        <v>1106873598.954988</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>512826939.5976719</v>
+        <v>326430163.2321123</v>
       </c>
       <c r="E24" t="n">
-        <v>93942183.66001469</v>
+        <v>46857798.96902738</v>
       </c>
       <c r="F24" t="n">
-        <v>606769123.2576867</v>
+        <v>373287962.2011397</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>606769123.2576867</v>
+        <v>373287962.2011397</v>
       </c>
     </row>
     <row r="25">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>231951716.8009863</v>
+        <v>193967840.6387744</v>
       </c>
       <c r="F25" t="n">
-        <v>231951716.8009863</v>
+        <v>193967840.6387744</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>231951716.8009863</v>
+        <v>193967840.6387744</v>
       </c>
     </row>
     <row r="26">
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-250602138.3130837</v>
+        <v>-244585457.4665864</v>
       </c>
       <c r="F26" t="n">
-        <v>-250602138.3130837</v>
+        <v>-244585457.4665864</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-250602138.3130837</v>
+        <v>-244585457.4665864</v>
       </c>
     </row>
     <row r="27">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1826106748.523909</v>
+        <v>1829965788.967272</v>
       </c>
       <c r="E27" t="n">
-        <v>560400874.1863053</v>
+        <v>562080426.4404492</v>
       </c>
       <c r="F27" t="n">
-        <v>2386507622.710215</v>
+        <v>2392046215.407722</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2386507622.710215</v>
+        <v>2392046215.407722</v>
       </c>
     </row>
     <row r="28">
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3217279872.432061</v>
+        <v>3230946282.104176</v>
       </c>
       <c r="E28" t="n">
-        <v>1255980480.195157</v>
+        <v>1245099552.936992</v>
       </c>
       <c r="F28" t="n">
-        <v>4473260352.627217</v>
+        <v>4476045835.041168</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4473260352.627217</v>
+        <v>4476045835.041168</v>
       </c>
     </row>
     <row r="29">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-2892803078.898238</v>
+        <v>-2898069824.98115</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-2892803078.898238</v>
+        <v>-2898069824.98115</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-2892803078.898238</v>
+        <v>-2898069824.98115</v>
       </c>
     </row>
     <row r="30">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1502266857.173224</v>
+        <v>-1503579610.51945</v>
       </c>
       <c r="E30" t="n">
-        <v>-88033049.57662189</v>
+        <v>-88065414.00512807</v>
       </c>
       <c r="F30" t="n">
-        <v>-1590299906.749846</v>
+        <v>-1591645024.524578</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-1590299906.749846</v>
+        <v>-1591645024.524578</v>
       </c>
     </row>
     <row r="31">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-1500715085.193099</v>
+        <v>-1502359923.258183</v>
       </c>
       <c r="E31" t="n">
-        <v>-67272919.76085947</v>
+        <v>-67319034.01998186</v>
       </c>
       <c r="F31" t="n">
-        <v>-1567988004.953959</v>
+        <v>-1569678957.278165</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1567988004.953959</v>
+        <v>-1569678957.278165</v>
       </c>
     </row>
     <row r="32">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1079449621.754515</v>
+        <v>970674640.790839</v>
       </c>
       <c r="E32" t="n">
-        <v>199292876.9890093</v>
+        <v>193349948.7689836</v>
       </c>
       <c r="F32" t="n">
-        <v>1278742498.743524</v>
+        <v>1164024589.559823</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1278742498.743524</v>
+        <v>1164024589.559823</v>
       </c>
     </row>
     <row r="33">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>533643017.0907862</v>
+        <v>334735585.8661783</v>
       </c>
       <c r="E33" t="n">
-        <v>67739350.30410285</v>
+        <v>35116708.9503255</v>
       </c>
       <c r="F33" t="n">
-        <v>601382367.394889</v>
+        <v>369852294.8165038</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>601382367.394889</v>
+        <v>369852294.8165038</v>
       </c>
     </row>
     <row r="34">
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>234863905.2277696</v>
+        <v>196275252.2720836</v>
       </c>
       <c r="F34" t="n">
-        <v>234863905.2277696</v>
+        <v>196275252.2720836</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>234863905.2277696</v>
+        <v>196275252.2720836</v>
       </c>
     </row>
     <row r="35">
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-173508641.9408788</v>
+        <v>-181907699.0576614</v>
       </c>
       <c r="F35" t="n">
-        <v>-173508641.9408788</v>
+        <v>-181907699.0576614</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-173508641.9408788</v>
+        <v>-181907699.0576614</v>
       </c>
     </row>
     <row r="36">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1920903864.190894</v>
+        <v>1924918822.438825</v>
       </c>
       <c r="E36" t="n">
-        <v>578375801.3371502</v>
+        <v>580140458.7122216</v>
       </c>
       <c r="F36" t="n">
-        <v>2499279665.528044</v>
+        <v>2505059281.151046</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2499279665.528044</v>
+        <v>2505059281.151046</v>
       </c>
     </row>
     <row r="37">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3438827012.264998</v>
+        <v>3452874622.446946</v>
       </c>
       <c r="E37" t="n">
-        <v>1022223397.274345</v>
+        <v>1011312201.184338</v>
       </c>
       <c r="F37" t="n">
-        <v>4461050409.539343</v>
+        <v>4464186823.631284</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4461050409.539343</v>
+        <v>4464186823.631284</v>
       </c>
     </row>
     <row r="38">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-2823950121.560254</v>
+        <v>-2828980981.514099</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-2823950121.560254</v>
+        <v>-2828980981.514099</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-2823950121.560254</v>
+        <v>-2828980981.514099</v>
       </c>
     </row>
     <row r="39">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1484427782.146688</v>
+        <v>-1485719149.512565</v>
       </c>
       <c r="E39" t="n">
-        <v>-87416666.97081165</v>
+        <v>-87448574.21145189</v>
       </c>
       <c r="F39" t="n">
-        <v>-1571844449.1175</v>
+        <v>-1573167723.724016</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-1571844449.1175</v>
+        <v>-1573167723.724016</v>
       </c>
     </row>
     <row r="40">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1480090213.710917</v>
+        <v>-1481693248.090842</v>
       </c>
       <c r="E40" t="n">
-        <v>-79507650.93301579</v>
+        <v>-79563595.75534216</v>
       </c>
       <c r="F40" t="n">
-        <v>-1559597864.643933</v>
+        <v>-1561256843.846184</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>-1559597864.643933</v>
+        <v>-1561256843.846184</v>
       </c>
     </row>
     <row r="41">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1053041223.126753</v>
+        <v>941315241.1942489</v>
       </c>
       <c r="E41" t="n">
-        <v>195788025.1981952</v>
+        <v>189315182.4043921</v>
       </c>
       <c r="F41" t="n">
-        <v>1248829248.324949</v>
+        <v>1130630423.598641</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1248829248.324949</v>
+        <v>1130630423.598641</v>
       </c>
     </row>
     <row r="42">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>520369633.7373804</v>
+        <v>328643044.2391157</v>
       </c>
       <c r="E42" t="n">
-        <v>79240918.93445104</v>
+        <v>40103653.90342262</v>
       </c>
       <c r="F42" t="n">
-        <v>599610552.6718315</v>
+        <v>368746698.1425383</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>599610552.6718315</v>
+        <v>368746698.1425383</v>
       </c>
     </row>
     <row r="43">
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>231523105.7736381</v>
+        <v>193540206.4021482</v>
       </c>
       <c r="F43" t="n">
-        <v>231523105.7736381</v>
+        <v>193540206.4021482</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>231523105.7736381</v>
+        <v>193540206.4021482</v>
       </c>
     </row>
     <row r="44">
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-214715593.5455545</v>
+        <v>-216063735.8948217</v>
       </c>
       <c r="F44" t="n">
-        <v>-214715593.5455545</v>
+        <v>-216063735.8948217</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-214715593.5455545</v>
+        <v>-216063735.8948217</v>
       </c>
     </row>
     <row r="45">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1865913055.941358</v>
+        <v>1869848788.996442</v>
       </c>
       <c r="E45" t="n">
-        <v>566154791.9938717</v>
+        <v>567869159.9707233</v>
       </c>
       <c r="F45" t="n">
-        <v>2432067847.93523</v>
+        <v>2437717948.967165</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2432067847.93523</v>
+        <v>2437717948.967165</v>
       </c>
     </row>
     <row r="46">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3317816108.356492</v>
+        <v>3331606199.803592</v>
       </c>
       <c r="E46" t="n">
-        <v>1125443036.759046</v>
+        <v>1114628303.452248</v>
       </c>
       <c r="F46" t="n">
-        <v>4443259145.115538</v>
+        <v>4446234503.255839</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4443259145.115538</v>
+        <v>4446234503.255839</v>
       </c>
     </row>
     <row r="47">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-2850201929.012933</v>
+        <v>-2855268888.074034</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-2850201929.012933</v>
+        <v>-2855268888.074034</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-2850201929.012933</v>
+        <v>-2855268888.074034</v>
       </c>
     </row>
     <row r="48">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1518592791.667027</v>
+        <v>-1519913156.083462</v>
       </c>
       <c r="E48" t="n">
-        <v>-89196313.61769548</v>
+        <v>-89228971.64735198</v>
       </c>
       <c r="F48" t="n">
-        <v>-1607789105.284723</v>
+        <v>-1609142127.730814</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>-1607789105.284723</v>
+        <v>-1609142127.730814</v>
       </c>
     </row>
     <row r="49">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1501277315.229708</v>
+        <v>-1502905845.684578</v>
       </c>
       <c r="E49" t="n">
-        <v>-67331143.89183764</v>
+        <v>-67395564.38218579</v>
       </c>
       <c r="F49" t="n">
-        <v>-1568608459.121546</v>
+        <v>-1570301410.066764</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1568608459.121546</v>
+        <v>-1570301410.066764</v>
       </c>
     </row>
     <row r="50">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1069184728.843646</v>
+        <v>953915290.4645797</v>
       </c>
       <c r="E50" t="n">
-        <v>199127253.849196</v>
+        <v>192642209.7906418</v>
       </c>
       <c r="F50" t="n">
-        <v>1268311982.692842</v>
+        <v>1146557500.255222</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1268311982.692842</v>
+        <v>1146557500.255222</v>
       </c>
     </row>
     <row r="51">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>529042882.7316132</v>
+        <v>333904534.6795402</v>
       </c>
       <c r="E51" t="n">
-        <v>80425193.85123558</v>
+        <v>41073509.15706834</v>
       </c>
       <c r="F51" t="n">
-        <v>609468076.5828488</v>
+        <v>374978043.8366085</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>609468076.5828488</v>
+        <v>374978043.8366085</v>
       </c>
     </row>
     <row r="52">
@@ -2358,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>236202807.0962931</v>
+        <v>197454131.6721421</v>
       </c>
       <c r="F52" t="n">
-        <v>236202807.0962931</v>
+        <v>197454131.6721421</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>236202807.0962931</v>
+        <v>197454131.6721421</v>
       </c>
     </row>
     <row r="53">
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>-201069936.43319</v>
+        <v>-203416267.7451056</v>
       </c>
       <c r="F53" t="n">
-        <v>-201069936.43319</v>
+        <v>-203416267.7451056</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-201069936.43319</v>
+        <v>-203416267.7451056</v>
       </c>
     </row>
     <row r="54">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1890848440.179662</v>
+        <v>1894798207.770339</v>
       </c>
       <c r="E54" t="n">
-        <v>575161723.7373053</v>
+        <v>576901289.4294164</v>
       </c>
       <c r="F54" t="n">
-        <v>2466010163.916968</v>
+        <v>2471699497.199755</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2466010163.916968</v>
+        <v>2471699497.199755</v>
       </c>
     </row>
     <row r="55">
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3356961299.75534</v>
+        <v>3370963813.785583</v>
       </c>
       <c r="E55" t="n">
-        <v>1139828758.864909</v>
+        <v>1128795126.66231</v>
       </c>
       <c r="F55" t="n">
-        <v>4496790058.620248</v>
+        <v>4499758940.447893</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4496790058.620248</v>
+        <v>4499758940.447893</v>
       </c>
     </row>
     <row r="56">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2899717606.748238</v>
+        <v>-2904978033.370792</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-2899717606.748238</v>
+        <v>-2904978033.370792</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>-2899717606.748238</v>
+        <v>-2904978033.370792</v>
       </c>
     </row>
     <row r="57">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1519301097.610961</v>
+        <v>-1520627674.7663</v>
       </c>
       <c r="E57" t="n">
-        <v>-88952311.92939194</v>
+        <v>-88985044.25020009</v>
       </c>
       <c r="F57" t="n">
-        <v>-1608253409.540353</v>
+        <v>-1609612719.0165</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>-1608253409.540353</v>
+        <v>-1609612719.0165</v>
       </c>
     </row>
     <row r="58">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1510247230.276803</v>
+        <v>-1511901728.280483</v>
       </c>
       <c r="E58" t="n">
-        <v>-61835301.53727505</v>
+        <v>-61887173.11008355</v>
       </c>
       <c r="F58" t="n">
-        <v>-1572082531.814079</v>
+        <v>-1573788901.390567</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>-1572082531.814079</v>
+        <v>-1573788901.390567</v>
       </c>
     </row>
     <row r="59">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1085507522.92363</v>
+        <v>974437567.7038515</v>
       </c>
       <c r="E59" t="n">
-        <v>200763212.83173</v>
+        <v>194756216.1749827</v>
       </c>
       <c r="F59" t="n">
-        <v>1286270735.75536</v>
+        <v>1169193783.878834</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1286270735.75536</v>
+        <v>1169193783.878834</v>
       </c>
     </row>
     <row r="60">
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>537038850.6102486</v>
+        <v>336990611.6534101</v>
       </c>
       <c r="E60" t="n">
-        <v>69601404.42702724</v>
+        <v>36186933.31815184</v>
       </c>
       <c r="F60" t="n">
-        <v>606640255.0372758</v>
+        <v>373177544.971562</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>606640255.0372758</v>
+        <v>373177544.971562</v>
       </c>
     </row>
     <row r="61">
@@ -2664,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>237100266.3066151</v>
+        <v>198151952.156349</v>
       </c>
       <c r="F61" t="n">
-        <v>237100266.3066151</v>
+        <v>198151952.156349</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>237100266.3066151</v>
+        <v>198151952.156349</v>
       </c>
     </row>
     <row r="62">
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-170297515.8426302</v>
+        <v>-178503779.9571419</v>
       </c>
       <c r="F62" t="n">
-        <v>-170297515.8426302</v>
+        <v>-178503779.9571419</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>-170297515.8426302</v>
+        <v>-178503779.9571419</v>
       </c>
     </row>
     <row r="63">
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1928647122.516229</v>
+        <v>1932660886.371517</v>
       </c>
       <c r="E63" t="n">
-        <v>582032069.7271385</v>
+        <v>583805212.310558</v>
       </c>
       <c r="F63" t="n">
-        <v>2510679192.243367</v>
+        <v>2516466098.682075</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2510679192.243367</v>
+        <v>2516466098.682075</v>
       </c>
     </row>
     <row r="64">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3447003500.187933</v>
+        <v>3461142416.206189</v>
       </c>
       <c r="E64" t="n">
-        <v>1041635687.089756</v>
+        <v>1030611728.743424</v>
       </c>
       <c r="F64" t="n">
-        <v>4488639187.277689</v>
+        <v>4491754144.949613</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4488639187.277689</v>
+        <v>4491754144.949613</v>
       </c>
     </row>
   </sheetData>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>752058738.2040737</v>
+        <v>465345192.4220803</v>
       </c>
       <c r="C2" t="n">
-        <v>1917804452.015082</v>
+        <v>1824231668.883123</v>
       </c>
       <c r="D2" t="n">
-        <v>2669863190.219156</v>
+        <v>2289576861.305203</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-98150409.30371809</v>
+        <v>-134741169.3209324</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.452800516873228</v>
+        <v>-8.421323082558274</v>
       </c>
       <c r="H2" t="n">
-        <v>-98150409.30371809</v>
+        <v>-134741169.3209324</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.452800516873228</v>
+        <v>-8.421323082558274</v>
       </c>
     </row>
     <row r="3">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1223921918.739581</v>
+        <v>916444004.9789721</v>
       </c>
       <c r="C3" t="n">
-        <v>1751650437.335064</v>
+        <v>1654490758.734831</v>
       </c>
       <c r="D3" t="n">
-        <v>2975572356.074646</v>
+        <v>2570934763.713802</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>207558756.5517716</v>
+        <v>146616733.0876665</v>
       </c>
       <c r="G3" t="n">
-        <v>11.53104203065398</v>
+        <v>9.163545817979157</v>
       </c>
       <c r="H3" t="n">
-        <v>103779378.2758858</v>
+        <v>73308366.54383326</v>
       </c>
       <c r="I3" t="n">
-        <v>5.76552101532699</v>
+        <v>4.581772908989579</v>
       </c>
     </row>
     <row r="4">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>853294446.459373</v>
+        <v>558382947.2380811</v>
       </c>
       <c r="C4" t="n">
-        <v>1915622478.240789</v>
+        <v>1820161228.20051</v>
       </c>
       <c r="D4" t="n">
-        <v>2768916924.700162</v>
+        <v>2378544175.43859</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>903325.1772880554</v>
+        <v>-45773855.18754578</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05018473207155864</v>
+        <v>-2.860865949221611</v>
       </c>
       <c r="H4" t="n">
-        <v>451662.5886440277</v>
+        <v>-45773855.18754578</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02509236603577932</v>
+        <v>-2.860865949221611</v>
       </c>
     </row>
     <row r="5">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1077038494.036631</v>
+        <v>779194312.784005</v>
       </c>
       <c r="C5" t="n">
-        <v>1773680719.854016</v>
+        <v>1678902422.805181</v>
       </c>
       <c r="D5" t="n">
-        <v>2850719213.890648</v>
+        <v>2458096735.589186</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82705614.36777401</v>
+        <v>33778704.96305037</v>
       </c>
       <c r="G5" t="n">
-        <v>4.594756353765223</v>
+        <v>2.111169060190648</v>
       </c>
       <c r="H5" t="n">
-        <v>41352807.183887</v>
+        <v>16889352.48152518</v>
       </c>
       <c r="I5" t="n">
-        <v>2.297378176882611</v>
+        <v>1.055584530095324</v>
       </c>
     </row>
     <row r="6">
@@ -2980,13 +2980,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>968671903.7441241</v>
+        <v>675019895.1158938</v>
       </c>
       <c r="C6" t="n">
-        <v>1816509967.20982</v>
+        <v>1722380600.271318</v>
       </c>
       <c r="D6" t="n">
-        <v>2785181870.953945</v>
+        <v>2397400495.387212</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17168271.4310708</v>
+        <v>-26917535.23892403</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9537928572817114</v>
+        <v>-1.682345952432752</v>
       </c>
       <c r="H6" t="n">
-        <v>8584135.715535402</v>
+        <v>-26917535.23892403</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4768964286408557</v>
+        <v>-1.682345952432752</v>
       </c>
     </row>
     <row r="7">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>975965315.6005923</v>
+        <v>675493956.8579671</v>
       </c>
       <c r="C7" t="n">
-        <v>1873148343.456216</v>
+        <v>1776825462.936935</v>
       </c>
       <c r="D7" t="n">
-        <v>2849113659.056808</v>
+        <v>2452319419.794902</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3027,16 +3027,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>81100059.53393412</v>
+        <v>28001389.1687665</v>
       </c>
       <c r="G7" t="n">
-        <v>4.50555886299634</v>
+        <v>1.750086823047906</v>
       </c>
       <c r="H7" t="n">
-        <v>40550029.76696706</v>
+        <v>14000694.58438325</v>
       </c>
       <c r="I7" t="n">
-        <v>2.25277943149817</v>
+        <v>0.8750434115239532</v>
       </c>
     </row>
     <row r="8">
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1068931061.602039</v>
+        <v>767724045.517392</v>
       </c>
       <c r="C8" t="n">
-        <v>1810047511.07297</v>
+        <v>1714136045.38604</v>
       </c>
       <c r="D8" t="n">
-        <v>2878978572.675008</v>
+        <v>2481860090.903432</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>110964973.1521344</v>
+        <v>57542060.27729654</v>
       </c>
       <c r="G8" t="n">
-        <v>6.164720730674135</v>
+        <v>3.596378767331034</v>
       </c>
       <c r="H8" t="n">
-        <v>55482486.57606721</v>
+        <v>28771030.13864827</v>
       </c>
       <c r="I8" t="n">
-        <v>3.082360365337067</v>
+        <v>1.798189383665517</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/eve_results.xlsx
+++ b/irrbb_calc/output/eve_results.xlsx
@@ -458,13 +458,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-5837029699.068525</v>
+        <v>-6875102919.94</v>
       </c>
       <c r="D2" t="n">
-        <v>-161844533.8616113</v>
+        <v>-95696510.04890218</v>
       </c>
       <c r="E2" t="n">
-        <v>-5998874232.930137</v>
+        <v>-6970799429.988902</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1278847057.85</v>
+        <v>1284728808.5</v>
       </c>
       <c r="D3" t="n">
-        <v>231584150.3581635</v>
+        <v>317328976.2060196</v>
       </c>
       <c r="E3" t="n">
-        <v>1510431208.208163</v>
+        <v>1602057784.706019</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +503,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-14336961.1800304</v>
+        <v>-8477827.203162251</v>
       </c>
       <c r="E4" t="n">
-        <v>-14336961.1800304</v>
+        <v>-8477827.203162251</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5233457764.944227</v>
+        <v>5736321506.339336</v>
       </c>
       <c r="D5" t="n">
-        <v>1693640251.583912</v>
+        <v>1815154595.930524</v>
       </c>
       <c r="E5" t="n">
-        <v>6927098016.528139</v>
+        <v>7551476102.26986</v>
       </c>
     </row>
   </sheetData>
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>675275123.7257019</v>
+        <v>145947394.8993364</v>
       </c>
       <c r="C2" t="n">
-        <v>1749042906.900434</v>
+        <v>2028309234.884479</v>
       </c>
       <c r="D2" t="n">
-        <v>2424318030.626136</v>
+        <v>2174256629.783815</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2695465919.310573</v>
+        <v>-3256778657.306471</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-2695465919.310573</v>
+        <v>-3256778657.306471</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2695465919.310573</v>
+        <v>-3256778657.306471</v>
       </c>
     </row>
     <row r="3">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1459014759.962479</v>
+        <v>-1763198912.999988</v>
       </c>
       <c r="E3" t="n">
-        <v>-86735165.71982653</v>
+        <v>-21094459.78994248</v>
       </c>
       <c r="F3" t="n">
-        <v>-1545749925.682306</v>
+        <v>-1784293372.78993</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1545749925.682306</v>
+        <v>-1784293372.78993</v>
       </c>
     </row>
     <row r="4">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1444967479.344626</v>
+        <v>-1641504292.978168</v>
       </c>
       <c r="E4" t="n">
-        <v>-101462878.7715522</v>
+        <v>-102234344.4614767</v>
       </c>
       <c r="F4" t="n">
-        <v>-1546430358.116178</v>
+        <v>-1743738637.439645</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-1546430358.116178</v>
+        <v>-1743738637.439645</v>
       </c>
     </row>
     <row r="5">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>884354622.0529087</v>
+        <v>956644164.5950364</v>
       </c>
       <c r="E5" t="n">
-        <v>181942076.7411945</v>
+        <v>222153197.0988902</v>
       </c>
       <c r="F5" t="n">
-        <v>1066296698.794103</v>
+        <v>1178797361.693927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1066296698.794103</v>
+        <v>1178797361.693927</v>
       </c>
     </row>
     <row r="6">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>317529440.6810989</v>
+        <v>225848751.8600489</v>
       </c>
       <c r="E6" t="n">
-        <v>51020927.52694491</v>
+        <v>111976446.1441714</v>
       </c>
       <c r="F6" t="n">
-        <v>368550368.2080438</v>
+        <v>337825198.0042203</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>368550368.2080438</v>
+        <v>337825198.0042203</v>
       </c>
     </row>
     <row r="7">
@@ -828,10 +828,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>189032198.9218521</v>
+        <v>48394700.73572497</v>
       </c>
       <c r="F7" t="n">
-        <v>189032198.9218521</v>
+        <v>48394700.73572497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>189032198.9218521</v>
+        <v>48394700.73572497</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-284716169.7502007</v>
+        <v>-79021734.3724252</v>
       </c>
       <c r="F8" t="n">
-        <v>-284716169.7502007</v>
+        <v>-79021734.3724252</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-284716169.7502007</v>
+        <v>-79021734.3724252</v>
       </c>
     </row>
     <row r="9">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1764517613.794478</v>
+        <v>1285144839.243104</v>
       </c>
       <c r="E9" t="n">
-        <v>545265787.1551471</v>
+        <v>371829556.977418</v>
       </c>
       <c r="F9" t="n">
-        <v>2309783400.949625</v>
+        <v>1656974396.220522</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2309783400.949625</v>
+        <v>1656974396.220522</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3098391674.511272</v>
+        <v>4049592445.46318</v>
       </c>
       <c r="E10" t="n">
-        <v>1329884892.779564</v>
+        <v>1681127984.795213</v>
       </c>
       <c r="F10" t="n">
-        <v>4428276567.290836</v>
+        <v>5730720430.258393</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4428276567.290836</v>
+        <v>5730720430.258393</v>
       </c>
     </row>
     <row r="11">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3004287080.358242</v>
+        <v>-3583423798.486528</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-3004287080.358242</v>
+        <v>-3583423798.486528</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3004287080.358242</v>
+        <v>-3583423798.486528</v>
       </c>
     </row>
     <row r="12">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1547967289.521232</v>
+        <v>-1785341587.331126</v>
       </c>
       <c r="E12" t="n">
-        <v>-89974597.74089299</v>
+        <v>-21446988.5773839</v>
       </c>
       <c r="F12" t="n">
-        <v>-1637941887.262125</v>
+        <v>-1806788575.90851</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-1637941887.262125</v>
+        <v>-1806788575.90851</v>
       </c>
     </row>
     <row r="13">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1542214172.839975</v>
+        <v>-1739236876.100953</v>
       </c>
       <c r="E13" t="n">
-        <v>-44136590.95281409</v>
+        <v>-44790854.62068366</v>
       </c>
       <c r="F13" t="n">
-        <v>-1586350763.792789</v>
+        <v>-1784027730.721637</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-1586350763.792789</v>
+        <v>-1784027730.721637</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1016494720.626164</v>
+        <v>1104221921.89758</v>
       </c>
       <c r="E14" t="n">
-        <v>200633258.7332544</v>
+        <v>244067509.8078884</v>
       </c>
       <c r="F14" t="n">
-        <v>1217127979.359418</v>
+        <v>1348289431.705469</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1217127979.359418</v>
+        <v>1348289431.705469</v>
       </c>
     </row>
     <row r="15">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>345848757.3690892</v>
+        <v>293779851.1165479</v>
       </c>
       <c r="E15" t="n">
-        <v>29333222.07038736</v>
+        <v>52898352.51548136</v>
       </c>
       <c r="F15" t="n">
-        <v>375181979.4394766</v>
+        <v>346678203.6320292</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>375181979.4394766</v>
+        <v>346678203.6320292</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>202242745.6677688</v>
+        <v>52406121.7652897</v>
       </c>
       <c r="F16" t="n">
-        <v>202242745.6677688</v>
+        <v>52406121.7652897</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>202242745.6677688</v>
+        <v>52406121.7652897</v>
       </c>
     </row>
     <row r="17">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-130116086.0134829</v>
+        <v>-37113337.26254971</v>
       </c>
       <c r="F17" t="n">
-        <v>-130116086.0134829</v>
+        <v>-37113337.26254971</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-130116086.0134829</v>
+        <v>-37113337.26254971</v>
       </c>
     </row>
     <row r="18">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2012072973.872798</v>
+        <v>1461071018.42212</v>
       </c>
       <c r="E18" t="n">
-        <v>601658611.9384332</v>
+        <v>409610981.5324987</v>
       </c>
       <c r="F18" t="n">
-        <v>2613731585.811231</v>
+        <v>1870681999.954619</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2613731585.811231</v>
+        <v>1870681999.954619</v>
       </c>
     </row>
     <row r="19">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3636496095.83037</v>
+        <v>4724371980.772829</v>
       </c>
       <c r="E19" t="n">
-        <v>884850195.0321769</v>
+        <v>1136138637.676569</v>
       </c>
       <c r="F19" t="n">
-        <v>4521346290.862547</v>
+        <v>5860510618.449398</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4521346290.862547</v>
+        <v>5860510618.449398</v>
       </c>
     </row>
     <row r="20">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-2774441796.51401</v>
+        <v>-3340433482.509024</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-2774441796.51401</v>
+        <v>-3340433482.509024</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-2774441796.51401</v>
+        <v>-3340433482.509024</v>
       </c>
     </row>
     <row r="21">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1496460323.905028</v>
+        <v>-1779809062.420523</v>
       </c>
       <c r="E21" t="n">
-        <v>-88382304.60151681</v>
+        <v>-21351087.73845858</v>
       </c>
       <c r="F21" t="n">
-        <v>-1584842628.506545</v>
+        <v>-1801160150.158982</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-1584842628.506545</v>
+        <v>-1801160150.158982</v>
       </c>
     </row>
     <row r="22">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1477214337.526204</v>
+        <v>-1674355105.551094</v>
       </c>
       <c r="E22" t="n">
-        <v>-82593056.79185569</v>
+        <v>-83373459.93998522</v>
       </c>
       <c r="F22" t="n">
-        <v>-1559807394.31806</v>
+        <v>-1757728565.491079</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>-1559807394.31806</v>
+        <v>-1757728565.491079</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>919157170.8797625</v>
+        <v>995367131.5699601</v>
       </c>
       <c r="E23" t="n">
-        <v>187716428.0752255</v>
+        <v>228842881.5594109</v>
       </c>
       <c r="F23" t="n">
-        <v>1106873598.954988</v>
+        <v>1224210013.129371</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1106873598.954988</v>
+        <v>1224210013.129371</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>326430163.2321123</v>
+        <v>240541711.6625783</v>
       </c>
       <c r="E24" t="n">
-        <v>46857798.96902738</v>
+        <v>103117791.2761761</v>
       </c>
       <c r="F24" t="n">
-        <v>373287962.2011397</v>
+        <v>343659502.9387544</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>373287962.2011397</v>
+        <v>343659502.9387544</v>
       </c>
     </row>
     <row r="25">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>193967840.6387744</v>
+        <v>49778513.82820629</v>
       </c>
       <c r="F25" t="n">
-        <v>193967840.6387744</v>
+        <v>49778513.82820629</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>193967840.6387744</v>
+        <v>49778513.82820629</v>
       </c>
     </row>
     <row r="26">
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-244585457.4665864</v>
+        <v>-70044998.98962246</v>
       </c>
       <c r="F26" t="n">
-        <v>-244585457.4665864</v>
+        <v>-70044998.98962246</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-244585457.4665864</v>
+        <v>-70044998.98962246</v>
       </c>
     </row>
     <row r="27">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1829965788.967272</v>
+        <v>1332083568.712087</v>
       </c>
       <c r="E27" t="n">
-        <v>562080426.4404492</v>
+        <v>383177640.415179</v>
       </c>
       <c r="F27" t="n">
-        <v>2392046215.407722</v>
+        <v>1715261209.127266</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2392046215.407722</v>
+        <v>1715261209.127266</v>
       </c>
     </row>
     <row r="28">
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3230946282.104176</v>
+        <v>4218012179.786539</v>
       </c>
       <c r="E28" t="n">
-        <v>1245099552.936992</v>
+        <v>1576812847.361132</v>
       </c>
       <c r="F28" t="n">
-        <v>4476045835.041168</v>
+        <v>5794825027.147671</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4476045835.041168</v>
+        <v>5794825027.147671</v>
       </c>
     </row>
     <row r="29">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-2898069824.98115</v>
+        <v>-3470957552.689276</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-2898069824.98115</v>
+        <v>-3470957552.689276</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-2898069824.98115</v>
+        <v>-3470957552.689276</v>
       </c>
     </row>
     <row r="30">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1503579610.51945</v>
+        <v>-1766716057.859257</v>
       </c>
       <c r="E30" t="n">
-        <v>-88065414.00512807</v>
+        <v>-21158734.396371</v>
       </c>
       <c r="F30" t="n">
-        <v>-1591645024.524578</v>
+        <v>-1787874792.255628</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-1591645024.524578</v>
+        <v>-1787874792.255628</v>
       </c>
     </row>
     <row r="31">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-1502359923.258183</v>
+        <v>-1698723691.342683</v>
       </c>
       <c r="E31" t="n">
-        <v>-67319034.01998186</v>
+        <v>-68138447.22528417</v>
       </c>
       <c r="F31" t="n">
-        <v>-1569678957.278165</v>
+        <v>-1766862138.567967</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1569678957.278165</v>
+        <v>-1766862138.567967</v>
       </c>
     </row>
     <row r="32">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>970674640.790839</v>
+        <v>1053022052.113768</v>
       </c>
       <c r="E32" t="n">
-        <v>193349948.7689836</v>
+        <v>235590924.785206</v>
       </c>
       <c r="F32" t="n">
-        <v>1164024589.559823</v>
+        <v>1288612976.898974</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1164024589.559823</v>
+        <v>1288612976.898974</v>
       </c>
     </row>
     <row r="33">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>334735585.8661783</v>
+        <v>272612670.7094528</v>
       </c>
       <c r="E33" t="n">
-        <v>35116708.9503255</v>
+        <v>67466217.2764869</v>
       </c>
       <c r="F33" t="n">
-        <v>369852294.8165038</v>
+        <v>340078887.9859397</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>369852294.8165038</v>
+        <v>340078887.9859397</v>
       </c>
     </row>
     <row r="34">
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>196275252.2720836</v>
+        <v>50710365.60704952</v>
       </c>
       <c r="F34" t="n">
-        <v>196275252.2720836</v>
+        <v>50710365.60704952</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>196275252.2720836</v>
+        <v>50710365.60704952</v>
       </c>
     </row>
     <row r="35">
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-181907699.0576614</v>
+        <v>-49260503.18581253</v>
       </c>
       <c r="F35" t="n">
-        <v>-181907699.0576614</v>
+        <v>-49260503.18581253</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-181907699.0576614</v>
+        <v>-49260503.18581253</v>
       </c>
     </row>
     <row r="36">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1924918822.438825</v>
+        <v>1398775318.730009</v>
       </c>
       <c r="E36" t="n">
-        <v>580140458.7122216</v>
+        <v>395116885.5672703</v>
       </c>
       <c r="F36" t="n">
-        <v>2505059281.151046</v>
+        <v>1793892204.29728</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2505059281.151046</v>
+        <v>1793892204.29728</v>
       </c>
     </row>
     <row r="37">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3452874622.446946</v>
+        <v>4492948496.507627</v>
       </c>
       <c r="E37" t="n">
-        <v>1011312201.184338</v>
+        <v>1290648058.261173</v>
       </c>
       <c r="F37" t="n">
-        <v>4464186823.631284</v>
+        <v>5783596554.768801</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4464186823.631284</v>
+        <v>5783596554.768801</v>
       </c>
     </row>
     <row r="38">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-2828980981.514099</v>
+        <v>-3397896505.289096</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-2828980981.514099</v>
+        <v>-3397896505.289096</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-2828980981.514099</v>
+        <v>-3397896505.289096</v>
       </c>
     </row>
     <row r="39">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1485719149.512565</v>
+        <v>-1763112731.422296</v>
       </c>
       <c r="E39" t="n">
-        <v>-87448574.21145189</v>
+        <v>-21100499.66340495</v>
       </c>
       <c r="F39" t="n">
-        <v>-1573167723.724016</v>
+        <v>-1784213231.085701</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-1573167723.724016</v>
+        <v>-1784213231.085701</v>
       </c>
     </row>
     <row r="40">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1481693248.090842</v>
+        <v>-1678005603.809977</v>
       </c>
       <c r="E40" t="n">
-        <v>-79563595.75534216</v>
+        <v>-80368350.91645695</v>
       </c>
       <c r="F40" t="n">
-        <v>-1561256843.846184</v>
+        <v>-1758373954.726434</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>-1561256843.846184</v>
+        <v>-1758373954.726434</v>
       </c>
     </row>
     <row r="41">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>941315241.1942489</v>
+        <v>1020206080.940479</v>
       </c>
       <c r="E41" t="n">
-        <v>189315182.4043921</v>
+        <v>230847513.6164317</v>
       </c>
       <c r="F41" t="n">
-        <v>1130630423.598641</v>
+        <v>1251053594.556911</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1130630423.598641</v>
+        <v>1251053594.556911</v>
       </c>
     </row>
     <row r="42">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>328643044.2391157</v>
+        <v>256991512.47607</v>
       </c>
       <c r="E42" t="n">
-        <v>40103653.90342262</v>
+        <v>81556417.10022967</v>
       </c>
       <c r="F42" t="n">
-        <v>368746698.1425383</v>
+        <v>338547929.5762996</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>368746698.1425383</v>
+        <v>338547929.5762996</v>
       </c>
     </row>
     <row r="43">
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>193540206.4021482</v>
+        <v>49865323.80716262</v>
       </c>
       <c r="F43" t="n">
-        <v>193540206.4021482</v>
+        <v>49865323.80716262</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>193540206.4021482</v>
+        <v>49865323.80716262</v>
       </c>
     </row>
     <row r="44">
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-216063735.8948217</v>
+        <v>-58772444.62583864</v>
       </c>
       <c r="F44" t="n">
-        <v>-216063735.8948217</v>
+        <v>-58772444.62583864</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-216063735.8948217</v>
+        <v>-58772444.62583864</v>
       </c>
     </row>
     <row r="45">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1869848788.996442</v>
+        <v>1359702828.361849</v>
       </c>
       <c r="E45" t="n">
-        <v>567869159.9707233</v>
+        <v>386906886.3134878</v>
       </c>
       <c r="F45" t="n">
-        <v>2437717948.967165</v>
+        <v>1746609714.675337</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2437717948.967165</v>
+        <v>1746609714.675337</v>
       </c>
     </row>
     <row r="46">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3331606199.803592</v>
+        <v>4341254252.794787</v>
       </c>
       <c r="E46" t="n">
-        <v>1114628303.452248</v>
+        <v>1417025437.412105</v>
       </c>
       <c r="F46" t="n">
-        <v>4446234503.255839</v>
+        <v>5758279690.206892</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4446234503.255839</v>
+        <v>5758279690.206892</v>
       </c>
     </row>
     <row r="47">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-2855268888.074034</v>
+        <v>-3425924546.32583</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-2855268888.074034</v>
+        <v>-3425924546.32583</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-2855268888.074034</v>
+        <v>-3425924546.32583</v>
       </c>
     </row>
     <row r="48">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1519913156.083462</v>
+        <v>-1785422281.217342</v>
       </c>
       <c r="E48" t="n">
-        <v>-89228971.64735198</v>
+        <v>-21440767.41358601</v>
       </c>
       <c r="F48" t="n">
-        <v>-1609142127.730814</v>
+        <v>-1806863048.630928</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>-1609142127.730814</v>
+        <v>-1806863048.630928</v>
       </c>
     </row>
     <row r="49">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1502905845.684578</v>
+        <v>-1700162088.542067</v>
       </c>
       <c r="E49" t="n">
-        <v>-67395564.38218579</v>
+        <v>-68192336.54847036</v>
       </c>
       <c r="F49" t="n">
-        <v>-1570301410.066764</v>
+        <v>-1768354425.090537</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1570301410.066764</v>
+        <v>-1768354425.090537</v>
       </c>
     </row>
     <row r="50">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>953915290.4645797</v>
+        <v>1034152271.827784</v>
       </c>
       <c r="E50" t="n">
-        <v>192642209.7906418</v>
+        <v>234613207.1805071</v>
       </c>
       <c r="F50" t="n">
-        <v>1146557500.255222</v>
+        <v>1268765479.008291</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1146557500.255222</v>
+        <v>1268765479.008291</v>
       </c>
     </row>
     <row r="51">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>333904534.6795402</v>
+        <v>258183705.0118565</v>
       </c>
       <c r="E51" t="n">
-        <v>41073509.15706834</v>
+        <v>87750169.35835026</v>
       </c>
       <c r="F51" t="n">
-        <v>374978043.8366085</v>
+        <v>345933874.3702068</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>374978043.8366085</v>
+        <v>345933874.3702068</v>
       </c>
     </row>
     <row r="52">
@@ -2358,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>197454131.6721421</v>
+        <v>50838711.81797314</v>
       </c>
       <c r="F52" t="n">
-        <v>197454131.6721421</v>
+        <v>50838711.81797314</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>197454131.6721421</v>
+        <v>50838711.81797314</v>
       </c>
     </row>
     <row r="53">
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>-203416267.7451056</v>
+        <v>-58878591.88523157</v>
       </c>
       <c r="F53" t="n">
-        <v>-203416267.7451056</v>
+        <v>-58878591.88523157</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-203416267.7451056</v>
+        <v>-58878591.88523157</v>
       </c>
     </row>
     <row r="54">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1894798207.770339</v>
+        <v>1378172954.719548</v>
       </c>
       <c r="E54" t="n">
-        <v>576901289.4294164</v>
+        <v>393108003.7875938</v>
       </c>
       <c r="F54" t="n">
-        <v>2471699497.199755</v>
+        <v>1771280958.507141</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2471699497.199755</v>
+        <v>1771280958.507141</v>
       </c>
     </row>
     <row r="55">
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3370963813.785583</v>
+        <v>4393845235.142068</v>
       </c>
       <c r="E55" t="n">
-        <v>1128795126.66231</v>
+        <v>1434164354.392908</v>
       </c>
       <c r="F55" t="n">
-        <v>4499758940.447893</v>
+        <v>5828009589.534976</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4499758940.447893</v>
+        <v>5828009589.534976</v>
       </c>
     </row>
     <row r="56">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2904978033.370792</v>
+        <v>-3478389930.401731</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-2904978033.370792</v>
+        <v>-3478389930.401731</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>-2904978033.370792</v>
+        <v>-3478389930.401731</v>
       </c>
     </row>
     <row r="57">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1520627674.7663</v>
+        <v>-1778660146.574771</v>
       </c>
       <c r="E57" t="n">
-        <v>-88985044.25020009</v>
+        <v>-21340537.19422145</v>
       </c>
       <c r="F57" t="n">
-        <v>-1609612719.0165</v>
+        <v>-1800000683.768992</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>-1609612719.0165</v>
+        <v>-1800000683.768992</v>
       </c>
     </row>
     <row r="58">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1511901728.280483</v>
+        <v>-1708782091.319164</v>
       </c>
       <c r="E58" t="n">
-        <v>-61887173.11008355</v>
+        <v>-62700575.33887476</v>
       </c>
       <c r="F58" t="n">
-        <v>-1573788901.390567</v>
+        <v>-1771482666.658039</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>-1573788901.390567</v>
+        <v>-1771482666.658039</v>
       </c>
     </row>
     <row r="59">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>974437567.7038515</v>
+        <v>1057149613.449686</v>
       </c>
       <c r="E59" t="n">
-        <v>194756216.1749827</v>
+        <v>237162249.3983841</v>
       </c>
       <c r="F59" t="n">
-        <v>1169193783.878834</v>
+        <v>1294311862.84807</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1169193783.878834</v>
+        <v>1294311862.84807</v>
       </c>
     </row>
     <row r="60">
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>336990611.6534101</v>
+        <v>271493772.2397426</v>
       </c>
       <c r="E60" t="n">
-        <v>36186933.31815184</v>
+        <v>72502667.67181981</v>
       </c>
       <c r="F60" t="n">
-        <v>373177544.971562</v>
+        <v>343996439.9115624</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>373177544.971562</v>
+        <v>343996439.9115624</v>
       </c>
     </row>
     <row r="61">
@@ -2664,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>198151952.156349</v>
+        <v>51159562.05996025</v>
       </c>
       <c r="F61" t="n">
-        <v>198151952.156349</v>
+        <v>51159562.05996025</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>198151952.156349</v>
+        <v>51159562.05996025</v>
       </c>
     </row>
     <row r="62">
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-178503779.9571419</v>
+        <v>-50327537.70444436</v>
       </c>
       <c r="F62" t="n">
-        <v>-178503779.9571419</v>
+        <v>-50327537.70444436</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>-178503779.9571419</v>
+        <v>-50327537.70444436</v>
       </c>
     </row>
     <row r="63">
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1932660886.371517</v>
+        <v>1404698533.360361</v>
       </c>
       <c r="E63" t="n">
-        <v>583805212.310558</v>
+        <v>397656888.5861675</v>
       </c>
       <c r="F63" t="n">
-        <v>2516466098.682075</v>
+        <v>1802355421.946528</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2516466098.682075</v>
+        <v>1802355421.946528</v>
       </c>
     </row>
     <row r="64">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3461142416.206189</v>
+        <v>4505195751.932012</v>
       </c>
       <c r="E64" t="n">
-        <v>1030611728.743424</v>
+        <v>1314111931.984749</v>
       </c>
       <c r="F64" t="n">
-        <v>4491754144.949613</v>
+        <v>5819307683.91676</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4491754144.949613</v>
+        <v>5819307683.91676</v>
       </c>
     </row>
   </sheetData>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>465345192.4220803</v>
+        <v>-144251662.1232575</v>
       </c>
       <c r="C2" t="n">
-        <v>1824231668.883123</v>
+        <v>2233131347.127573</v>
       </c>
       <c r="D2" t="n">
-        <v>2289576861.305203</v>
+        <v>2088879685.004316</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-134741169.3209324</v>
+        <v>-85376944.77949929</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.421323082558274</v>
+        <v>-7.114745398291608</v>
       </c>
       <c r="H2" t="n">
-        <v>-134741169.3209324</v>
+        <v>-85376944.77949929</v>
       </c>
       <c r="I2" t="n">
-        <v>-8.421323082558274</v>
+        <v>-7.114745398291608</v>
       </c>
     </row>
     <row r="3">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>916444004.9789721</v>
+        <v>475442510.2904696</v>
       </c>
       <c r="C3" t="n">
-        <v>1654490758.734831</v>
+        <v>1791770422.837109</v>
       </c>
       <c r="D3" t="n">
-        <v>2570934763.713802</v>
+        <v>2267212933.127579</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>146616733.0876665</v>
+        <v>92956303.34376431</v>
       </c>
       <c r="G3" t="n">
-        <v>9.163545817979157</v>
+        <v>7.746358611980359</v>
       </c>
       <c r="H3" t="n">
-        <v>73308366.54383326</v>
+        <v>46478151.67188215</v>
       </c>
       <c r="I3" t="n">
-        <v>4.581772908989579</v>
+        <v>3.873179305990179</v>
       </c>
     </row>
     <row r="4">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>558382947.2380811</v>
+        <v>-8593058.749476984</v>
       </c>
       <c r="C4" t="n">
-        <v>1820161228.20051</v>
+        <v>2166960127.772038</v>
       </c>
       <c r="D4" t="n">
-        <v>2378544175.43859</v>
+        <v>2158367069.022562</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-45773855.18754578</v>
+        <v>-15889560.76125336</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.860865949221611</v>
+        <v>-1.32413006343778</v>
       </c>
       <c r="H4" t="n">
-        <v>-45773855.18754578</v>
+        <v>-15889560.76125336</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.860865949221611</v>
+        <v>-1.32413006343778</v>
       </c>
     </row>
     <row r="5">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>779194312.784005</v>
+        <v>280961236.1696404</v>
       </c>
       <c r="C5" t="n">
-        <v>1678902422.805181</v>
+        <v>1900974766.689718</v>
       </c>
       <c r="D5" t="n">
-        <v>2458096735.589186</v>
+        <v>2181936002.859358</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33778704.96305037</v>
+        <v>7679373.075543404</v>
       </c>
       <c r="G5" t="n">
-        <v>2.111169060190648</v>
+        <v>0.6399477562952836</v>
       </c>
       <c r="H5" t="n">
-        <v>16889352.48152518</v>
+        <v>3839686.537771702</v>
       </c>
       <c r="I5" t="n">
-        <v>1.055584530095324</v>
+        <v>0.3199738781476418</v>
       </c>
     </row>
     <row r="6">
@@ -2980,13 +2980,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>675019895.1158938</v>
+        <v>139139834.0518155</v>
       </c>
       <c r="C6" t="n">
-        <v>1722380600.271318</v>
+        <v>2005960283.043716</v>
       </c>
       <c r="D6" t="n">
-        <v>2397400495.387212</v>
+        <v>2145100117.095532</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-26917535.23892403</v>
+        <v>-29156512.68828297</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.682345952432752</v>
+        <v>-2.429709390690247</v>
       </c>
       <c r="H6" t="n">
-        <v>-26917535.23892403</v>
+        <v>-29156512.68828297</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.682345952432752</v>
+        <v>-2.429709390690247</v>
       </c>
     </row>
     <row r="7">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>675493956.8579671</v>
+        <v>152845250.6160171</v>
       </c>
       <c r="C7" t="n">
-        <v>1776825462.936935</v>
+        <v>2051962750.690044</v>
       </c>
       <c r="D7" t="n">
-        <v>2452319419.794902</v>
+        <v>2204808001.306062</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3027,16 +3027,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>28001389.1687665</v>
+        <v>30551371.52224684</v>
       </c>
       <c r="G7" t="n">
-        <v>1.750086823047906</v>
+        <v>2.545947626853903</v>
       </c>
       <c r="H7" t="n">
-        <v>14000694.58438325</v>
+        <v>15275685.76112342</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8750434115239532</v>
+        <v>1.272973813426952</v>
       </c>
     </row>
     <row r="8">
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>767724045.517392</v>
+        <v>272705502.6861358</v>
       </c>
       <c r="C8" t="n">
-        <v>1714136045.38604</v>
+        <v>1938224649.46354</v>
       </c>
       <c r="D8" t="n">
-        <v>2481860090.903432</v>
+        <v>2210930152.149676</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>57542060.27729654</v>
+        <v>36673522.36586094</v>
       </c>
       <c r="G8" t="n">
-        <v>3.596378767331034</v>
+        <v>3.056126863821745</v>
       </c>
       <c r="H8" t="n">
-        <v>28771030.13864827</v>
+        <v>18336761.18293047</v>
       </c>
       <c r="I8" t="n">
-        <v>1.798189383665517</v>
+        <v>1.528063431910873</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/eve_results.xlsx
+++ b/irrbb_calc/output/eve_results.xlsx
@@ -458,13 +458,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-6875102919.94</v>
+        <v>-6888942153.225</v>
       </c>
       <c r="D2" t="n">
-        <v>-95696510.04890218</v>
+        <v>-95574548.38871074</v>
       </c>
       <c r="E2" t="n">
-        <v>-6970799429.988902</v>
+        <v>-6984516701.61371</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1284728808.5</v>
+        <v>1462419213.865</v>
       </c>
       <c r="D3" t="n">
-        <v>317328976.2060196</v>
+        <v>172538778.3262466</v>
       </c>
       <c r="E3" t="n">
-        <v>1602057784.706019</v>
+        <v>1634957992.191247</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +503,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-8477827.203162251</v>
+        <v>-6667024.314525582</v>
       </c>
       <c r="E4" t="n">
-        <v>-8477827.203162251</v>
+        <v>-6667024.314525582</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5736321506.339336</v>
+        <v>5761171342.164854</v>
       </c>
       <c r="D5" t="n">
-        <v>1815154595.930524</v>
+        <v>1787301534.276521</v>
       </c>
       <c r="E5" t="n">
-        <v>7551476102.26986</v>
+        <v>7548472876.441375</v>
       </c>
     </row>
   </sheetData>
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>145947394.8993364</v>
+        <v>334648402.8048539</v>
       </c>
       <c r="C2" t="n">
-        <v>2028309234.884479</v>
+        <v>1857598739.899531</v>
       </c>
       <c r="D2" t="n">
-        <v>2174256629.783815</v>
+        <v>2192247142.704385</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3256778657.306471</v>
+        <v>-3266226781.875385</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-3256778657.306471</v>
+        <v>-3266226781.875385</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-3256778657.306471</v>
+        <v>-3266226781.875385</v>
       </c>
     </row>
     <row r="3">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1763198912.999988</v>
+        <v>-1763101306.462626</v>
       </c>
       <c r="E3" t="n">
-        <v>-21094459.78994248</v>
+        <v>-21149120.47938829</v>
       </c>
       <c r="F3" t="n">
-        <v>-1784293372.78993</v>
+        <v>-1784250426.942014</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1784293372.78993</v>
+        <v>-1784250426.942014</v>
       </c>
     </row>
     <row r="4">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1641504292.978168</v>
+        <v>-1644897139.926168</v>
       </c>
       <c r="E4" t="n">
-        <v>-102234344.4614767</v>
+        <v>-102095128.5477959</v>
       </c>
       <c r="F4" t="n">
-        <v>-1743738637.439645</v>
+        <v>-1746992268.473964</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-1743738637.439645</v>
+        <v>-1746992268.473964</v>
       </c>
     </row>
     <row r="5">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>956644164.5950364</v>
+        <v>1034037645.955366</v>
       </c>
       <c r="E5" t="n">
-        <v>222153197.0988902</v>
+        <v>147970901.3942873</v>
       </c>
       <c r="F5" t="n">
-        <v>1178797361.693927</v>
+        <v>1182008547.349654</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1178797361.693927</v>
+        <v>1182008547.349654</v>
       </c>
     </row>
     <row r="6">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>225848751.8600489</v>
+        <v>369225148.204857</v>
       </c>
       <c r="E6" t="n">
-        <v>111976446.1441714</v>
+        <v>25234324.21323526</v>
       </c>
       <c r="F6" t="n">
-        <v>337825198.0042203</v>
+        <v>394459472.4180922</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>337825198.0042203</v>
+        <v>394459472.4180922</v>
       </c>
     </row>
     <row r="7">
@@ -828,10 +828,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>48394700.73572497</v>
+        <v>48510363.61575694</v>
       </c>
       <c r="F7" t="n">
-        <v>48394700.73572497</v>
+        <v>48510363.61575694</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>48394700.73572497</v>
+        <v>48510363.61575694</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-79021734.3724252</v>
+        <v>-77437894.22171178</v>
       </c>
       <c r="F8" t="n">
-        <v>-79021734.3724252</v>
+        <v>-77437894.22171178</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-79021734.3724252</v>
+        <v>-77437894.22171178</v>
       </c>
     </row>
     <row r="9">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1285144839.243104</v>
+        <v>1290284599.41296</v>
       </c>
       <c r="E9" t="n">
-        <v>371829556.977418</v>
+        <v>371091066.5848168</v>
       </c>
       <c r="F9" t="n">
-        <v>1656974396.220522</v>
+        <v>1661375665.997777</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1656974396.220522</v>
+        <v>1661375665.997777</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4049592445.46318</v>
+        <v>4070000592.711449</v>
       </c>
       <c r="E10" t="n">
-        <v>1681127984.795213</v>
+        <v>1654348281.386654</v>
       </c>
       <c r="F10" t="n">
-        <v>5730720430.258393</v>
+        <v>5724348874.098104</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5730720430.258393</v>
+        <v>5724348874.098104</v>
       </c>
     </row>
     <row r="11">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3583423798.486528</v>
+        <v>-3595018797.100747</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-3583423798.486528</v>
+        <v>-3595018797.100747</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3583423798.486528</v>
+        <v>-3595018797.100747</v>
       </c>
     </row>
     <row r="12">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1785341587.331126</v>
+        <v>-1785303105.702563</v>
       </c>
       <c r="E12" t="n">
-        <v>-21446988.5773839</v>
+        <v>-21503393.44474231</v>
       </c>
       <c r="F12" t="n">
-        <v>-1806788575.90851</v>
+        <v>-1806806499.147305</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-1806788575.90851</v>
+        <v>-1806806499.147305</v>
       </c>
     </row>
     <row r="13">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1739236876.100953</v>
+        <v>-1742750122.204495</v>
       </c>
       <c r="E13" t="n">
-        <v>-44790854.62068366</v>
+        <v>-45009890.26630468</v>
       </c>
       <c r="F13" t="n">
-        <v>-1784027730.721637</v>
+        <v>-1787760012.470799</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-1784027730.721637</v>
+        <v>-1787760012.470799</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1104221921.89758</v>
+        <v>1137390921.40021</v>
       </c>
       <c r="E14" t="n">
-        <v>244067509.8078884</v>
+        <v>162957026.400852</v>
       </c>
       <c r="F14" t="n">
-        <v>1348289431.705469</v>
+        <v>1300347947.801062</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1348289431.705469</v>
+        <v>1300347947.801062</v>
       </c>
     </row>
     <row r="15">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>293779851.1165479</v>
+        <v>388839345.5165195</v>
       </c>
       <c r="E15" t="n">
-        <v>52898352.51548136</v>
+        <v>9517205.231710548</v>
       </c>
       <c r="F15" t="n">
-        <v>346678203.6320292</v>
+        <v>398356550.74823</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>346678203.6320292</v>
+        <v>398356550.74823</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>52406121.7652897</v>
+        <v>52535642.07256661</v>
       </c>
       <c r="F16" t="n">
-        <v>52406121.7652897</v>
+        <v>52535642.07256661</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>52406121.7652897</v>
+        <v>52535642.07256661</v>
       </c>
     </row>
     <row r="17">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-37113337.26254971</v>
+        <v>-35309118.0728855</v>
       </c>
       <c r="F17" t="n">
-        <v>-37113337.26254971</v>
+        <v>-35309118.0728855</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-37113337.26254971</v>
+        <v>-35309118.0728855</v>
       </c>
     </row>
     <row r="18">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1461071018.42212</v>
+        <v>1466801922.604962</v>
       </c>
       <c r="E18" t="n">
-        <v>409610981.5324987</v>
+        <v>408885959.6564559</v>
       </c>
       <c r="F18" t="n">
-        <v>1870681999.954619</v>
+        <v>1875687882.261418</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1870681999.954619</v>
+        <v>1875687882.261418</v>
       </c>
     </row>
     <row r="19">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4724371980.772829</v>
+        <v>4742351944.18994</v>
       </c>
       <c r="E19" t="n">
-        <v>1136138637.676569</v>
+        <v>1109267477.863008</v>
       </c>
       <c r="F19" t="n">
-        <v>5860510618.449398</v>
+        <v>5851619422.052948</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5860510618.449398</v>
+        <v>5851619422.052948</v>
       </c>
     </row>
     <row r="20">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3340433482.509024</v>
+        <v>-3350370224.440778</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-3340433482.509024</v>
+        <v>-3350370224.440778</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-3340433482.509024</v>
+        <v>-3350370224.440778</v>
       </c>
     </row>
     <row r="21">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1779809062.420523</v>
+        <v>-1779746658.917952</v>
       </c>
       <c r="E21" t="n">
-        <v>-21351087.73845858</v>
+        <v>-21406898.03703971</v>
       </c>
       <c r="F21" t="n">
-        <v>-1801160150.158982</v>
+        <v>-1801153556.954991</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-1801160150.158982</v>
+        <v>-1801153556.954991</v>
       </c>
     </row>
     <row r="22">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1674355105.551094</v>
+        <v>-1677629089.713623</v>
       </c>
       <c r="E22" t="n">
-        <v>-83373459.93998522</v>
+        <v>-83224804.8379025</v>
       </c>
       <c r="F22" t="n">
-        <v>-1757728565.491079</v>
+        <v>-1760853894.551526</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>-1757728565.491079</v>
+        <v>-1760853894.551526</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>995367131.5699601</v>
+        <v>1061099376.039827</v>
       </c>
       <c r="E23" t="n">
-        <v>228842881.5594109</v>
+        <v>152607174.9130457</v>
       </c>
       <c r="F23" t="n">
-        <v>1224210013.129371</v>
+        <v>1213706550.952873</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1224210013.129371</v>
+        <v>1213706550.952873</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>240541711.6625783</v>
+        <v>378103073.8886718</v>
       </c>
       <c r="E24" t="n">
-        <v>103117791.2761761</v>
+        <v>19660348.80291696</v>
       </c>
       <c r="F24" t="n">
-        <v>343659502.9387544</v>
+        <v>397763422.6915888</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>343659502.9387544</v>
+        <v>397763422.6915888</v>
       </c>
     </row>
     <row r="25">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>49778513.82820629</v>
+        <v>49898248.72997621</v>
       </c>
       <c r="F25" t="n">
-        <v>49778513.82820629</v>
+        <v>49898248.72997621</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>49778513.82820629</v>
+        <v>49898248.72997621</v>
       </c>
     </row>
     <row r="26">
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-70044998.98962246</v>
+        <v>-68401471.02437343</v>
       </c>
       <c r="F26" t="n">
-        <v>-70044998.98962246</v>
+        <v>-68401471.02437343</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-70044998.98962246</v>
+        <v>-68401471.02437343</v>
       </c>
     </row>
     <row r="27">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1332083568.712087</v>
+        <v>1337385594.490246</v>
       </c>
       <c r="E27" t="n">
-        <v>383177640.415179</v>
+        <v>382430248.7819011</v>
       </c>
       <c r="F27" t="n">
-        <v>1715261209.127266</v>
+        <v>1719815843.272147</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1715261209.127266</v>
+        <v>1719815843.272147</v>
       </c>
     </row>
     <row r="28">
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4218012179.786539</v>
+        <v>4238216124.339675</v>
       </c>
       <c r="E28" t="n">
-        <v>1576812847.361132</v>
+        <v>1549714490.557562</v>
       </c>
       <c r="F28" t="n">
-        <v>5794825027.147671</v>
+        <v>5787930614.897237</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5794825027.147671</v>
+        <v>5787930614.897237</v>
       </c>
     </row>
     <row r="29">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-3470957552.689276</v>
+        <v>-3481869103.010223</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-3470957552.689276</v>
+        <v>-3481869103.010223</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-3470957552.689276</v>
+        <v>-3481869103.010223</v>
       </c>
     </row>
     <row r="30">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1766716057.859257</v>
+        <v>-1766637513.292219</v>
       </c>
       <c r="E30" t="n">
-        <v>-21158734.396371</v>
+        <v>-21213840.11837501</v>
       </c>
       <c r="F30" t="n">
-        <v>-1787874792.255628</v>
+        <v>-1787851353.410594</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-1787874792.255628</v>
+        <v>-1787851353.410594</v>
       </c>
     </row>
     <row r="31">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-1698723691.342683</v>
+        <v>-1702352079.45932</v>
       </c>
       <c r="E31" t="n">
-        <v>-68138447.22528417</v>
+        <v>-67934398.36046064</v>
       </c>
       <c r="F31" t="n">
-        <v>-1766862138.567967</v>
+        <v>-1770286477.819781</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1766862138.567967</v>
+        <v>-1770286477.819781</v>
       </c>
     </row>
     <row r="32">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1053022052.113768</v>
+        <v>1101677534.406734</v>
       </c>
       <c r="E32" t="n">
-        <v>235590924.785206</v>
+        <v>157104719.9201794</v>
       </c>
       <c r="F32" t="n">
-        <v>1288612976.898974</v>
+        <v>1258782254.326914</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1288612976.898974</v>
+        <v>1258782254.326914</v>
       </c>
     </row>
     <row r="33">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>272612670.7094528</v>
+        <v>378478669.4771072</v>
       </c>
       <c r="E33" t="n">
-        <v>67466217.2764869</v>
+        <v>16197755.8063393</v>
       </c>
       <c r="F33" t="n">
-        <v>340078887.9859397</v>
+        <v>394676425.2834465</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>340078887.9859397</v>
+        <v>394676425.2834465</v>
       </c>
     </row>
     <row r="34">
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>50710365.60704952</v>
+        <v>50834746.09217594</v>
       </c>
       <c r="F34" t="n">
-        <v>50710365.60704952</v>
+        <v>50834746.09217594</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>50710365.60704952</v>
+        <v>50834746.09217594</v>
       </c>
     </row>
     <row r="35">
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-49260503.18581253</v>
+        <v>-47533029.96106433</v>
       </c>
       <c r="F35" t="n">
-        <v>-49260503.18581253</v>
+        <v>-47533029.96106433</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-49260503.18581253</v>
+        <v>-47533029.96106433</v>
       </c>
     </row>
     <row r="36">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1398775318.730009</v>
+        <v>1404286294.030221</v>
       </c>
       <c r="E36" t="n">
-        <v>395116885.5672703</v>
+        <v>394398573.8916682</v>
       </c>
       <c r="F36" t="n">
-        <v>1793892204.29728</v>
+        <v>1798684867.92189</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1793892204.29728</v>
+        <v>1798684867.92189</v>
       </c>
     </row>
     <row r="37">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4492948496.507627</v>
+        <v>4511571712.967167</v>
       </c>
       <c r="E37" t="n">
-        <v>1290648058.261173</v>
+        <v>1263925756.763919</v>
       </c>
       <c r="F37" t="n">
-        <v>5783596554.768801</v>
+        <v>5775497469.731086</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5783596554.768801</v>
+        <v>5775497469.731086</v>
       </c>
     </row>
     <row r="38">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-3397896505.289096</v>
+        <v>-3408319333.568017</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-3397896505.289096</v>
+        <v>-3408319333.568017</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-3397896505.289096</v>
+        <v>-3408319333.568017</v>
       </c>
     </row>
     <row r="39">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1763112731.422296</v>
+        <v>-1763023548.783077</v>
       </c>
       <c r="E39" t="n">
-        <v>-21100499.66340495</v>
+        <v>-21155303.92068019</v>
       </c>
       <c r="F39" t="n">
-        <v>-1784213231.085701</v>
+        <v>-1784178852.703757</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-1784213231.085701</v>
+        <v>-1784178852.703757</v>
       </c>
     </row>
     <row r="40">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1678005603.809977</v>
+        <v>-1681589662.459445</v>
       </c>
       <c r="E40" t="n">
-        <v>-80368350.91645695</v>
+        <v>-80183693.33477247</v>
       </c>
       <c r="F40" t="n">
-        <v>-1758373954.726434</v>
+        <v>-1761773355.794217</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>-1758373954.726434</v>
+        <v>-1761773355.794217</v>
       </c>
     </row>
     <row r="41">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1020206080.940479</v>
+        <v>1078701226.475918</v>
       </c>
       <c r="E41" t="n">
-        <v>230847513.6164317</v>
+        <v>153870138.305684</v>
       </c>
       <c r="F41" t="n">
-        <v>1251053594.556911</v>
+        <v>1232571364.781602</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1251053594.556911</v>
+        <v>1232571364.781602</v>
       </c>
     </row>
     <row r="42">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>256991512.47607</v>
+        <v>374636825.6386479</v>
       </c>
       <c r="E42" t="n">
-        <v>81556417.10022967</v>
+        <v>19447147.64639056</v>
       </c>
       <c r="F42" t="n">
-        <v>338547929.5762996</v>
+        <v>394083973.2850384</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>338547929.5762996</v>
+        <v>394083973.2850384</v>
       </c>
     </row>
     <row r="43">
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>49865323.80716262</v>
+        <v>49986696.06493255</v>
       </c>
       <c r="F43" t="n">
-        <v>49865323.80716262</v>
+        <v>49986696.06493255</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>49865323.80716262</v>
+        <v>49986696.06493255</v>
       </c>
     </row>
     <row r="44">
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-58772444.62583864</v>
+        <v>-57093505.77639623</v>
       </c>
       <c r="F44" t="n">
-        <v>-58772444.62583864</v>
+        <v>-57093505.77639623</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-58772444.62583864</v>
+        <v>-57093505.77639623</v>
       </c>
     </row>
     <row r="45">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1359702828.361849</v>
+        <v>1365082572.829281</v>
       </c>
       <c r="E45" t="n">
-        <v>386906886.3134878</v>
+        <v>386183837.0818647</v>
       </c>
       <c r="F45" t="n">
-        <v>1746609714.675337</v>
+        <v>1751266409.911145</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1746609714.675337</v>
+        <v>1751266409.911145</v>
       </c>
     </row>
     <row r="46">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4341254252.794787</v>
+        <v>4360494846.589389</v>
       </c>
       <c r="E46" t="n">
-        <v>1417025437.412105</v>
+        <v>1390270267.893024</v>
       </c>
       <c r="F46" t="n">
-        <v>5758279690.206892</v>
+        <v>5750765114.482412</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5758279690.206892</v>
+        <v>5750765114.482412</v>
       </c>
     </row>
     <row r="47">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3425924546.32583</v>
+        <v>-3436422167.635112</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-3425924546.32583</v>
+        <v>-3436422167.635112</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-3425924546.32583</v>
+        <v>-3436422167.635112</v>
       </c>
     </row>
     <row r="48">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1785422281.217342</v>
+        <v>-1785375225.87358</v>
       </c>
       <c r="E48" t="n">
-        <v>-21440767.41358601</v>
+        <v>-21497026.15281431</v>
       </c>
       <c r="F48" t="n">
-        <v>-1806863048.630928</v>
+        <v>-1806872252.026394</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>-1806863048.630928</v>
+        <v>-1806872252.026394</v>
       </c>
     </row>
     <row r="49">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1700162088.542067</v>
+        <v>-1703472255.03539</v>
       </c>
       <c r="E49" t="n">
-        <v>-68192336.54847036</v>
+        <v>-68022275.66406374</v>
       </c>
       <c r="F49" t="n">
-        <v>-1768354425.090537</v>
+        <v>-1771494530.699454</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1768354425.090537</v>
+        <v>-1771494530.699454</v>
       </c>
     </row>
     <row r="50">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1034152271.827784</v>
+        <v>1088289858.372025</v>
       </c>
       <c r="E50" t="n">
-        <v>234613207.1805071</v>
+        <v>156555015.3044434</v>
       </c>
       <c r="F50" t="n">
-        <v>1268765479.008291</v>
+        <v>1244844873.676469</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1268765479.008291</v>
+        <v>1244844873.676469</v>
       </c>
     </row>
     <row r="51">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>258183705.0118565</v>
+        <v>383294129.9808388</v>
       </c>
       <c r="E51" t="n">
-        <v>87750169.35835026</v>
+        <v>15441583.74985308</v>
       </c>
       <c r="F51" t="n">
-        <v>345933874.3702068</v>
+        <v>398735713.7306919</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>345933874.3702068</v>
+        <v>398735713.7306919</v>
       </c>
     </row>
     <row r="52">
@@ -2358,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>50838711.81797314</v>
+        <v>50962119.71324782</v>
       </c>
       <c r="F52" t="n">
-        <v>50838711.81797314</v>
+        <v>50962119.71324782</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>50838711.81797314</v>
+        <v>50962119.71324782</v>
       </c>
     </row>
     <row r="53">
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>-58878591.88523157</v>
+        <v>-57176662.31307409</v>
       </c>
       <c r="F53" t="n">
-        <v>-58878591.88523157</v>
+        <v>-57176662.31307409</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-58878591.88523157</v>
+        <v>-57176662.31307409</v>
       </c>
     </row>
     <row r="54">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1378172954.719548</v>
+        <v>1383628247.441011</v>
       </c>
       <c r="E54" t="n">
-        <v>393108003.7875938</v>
+        <v>392363944.1245303</v>
       </c>
       <c r="F54" t="n">
-        <v>1771280958.507141</v>
+        <v>1775992191.565542</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1771280958.507141</v>
+        <v>1775992191.565542</v>
       </c>
     </row>
     <row r="55">
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4393845235.142068</v>
+        <v>4413469797.339037</v>
       </c>
       <c r="E55" t="n">
-        <v>1434164354.392908</v>
+        <v>1406998175.24365</v>
       </c>
       <c r="F55" t="n">
-        <v>5828009589.534976</v>
+        <v>5820467972.582687</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5828009589.534976</v>
+        <v>5820467972.582687</v>
       </c>
     </row>
     <row r="56">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-3478389930.401731</v>
+        <v>-3489288375.749453</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-3478389930.401731</v>
+        <v>-3489288375.749453</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>-3478389930.401731</v>
+        <v>-3489288375.749453</v>
       </c>
     </row>
     <row r="57">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1778660146.574771</v>
+        <v>-1778603733.837346</v>
       </c>
       <c r="E57" t="n">
-        <v>-21340537.19422145</v>
+        <v>-21396414.2172313</v>
       </c>
       <c r="F57" t="n">
-        <v>-1800000683.768992</v>
+        <v>-1800000148.054577</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>-1800000683.768992</v>
+        <v>-1800000148.054577</v>
       </c>
     </row>
     <row r="58">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1708782091.319164</v>
+        <v>-1712254318.096915</v>
       </c>
       <c r="E58" t="n">
-        <v>-62700575.33887476</v>
+        <v>-62506711.91301568</v>
       </c>
       <c r="F58" t="n">
-        <v>-1771482666.658039</v>
+        <v>-1774761030.009931</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>-1771482666.658039</v>
+        <v>-1774761030.009931</v>
       </c>
     </row>
     <row r="59">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1057149613.449686</v>
+        <v>1104480703.024926</v>
       </c>
       <c r="E59" t="n">
-        <v>237162249.3983841</v>
+        <v>158241827.4283697</v>
       </c>
       <c r="F59" t="n">
-        <v>1294311862.84807</v>
+        <v>1262722530.453295</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1294311862.84807</v>
+        <v>1262722530.453295</v>
       </c>
     </row>
     <row r="60">
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>271493772.2397426</v>
+        <v>382879853.8558538</v>
       </c>
       <c r="E60" t="n">
-        <v>72502667.67181981</v>
+        <v>14304251.23238228</v>
       </c>
       <c r="F60" t="n">
-        <v>343996439.9115624</v>
+        <v>397184105.088236</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>343996439.9115624</v>
+        <v>397184105.088236</v>
       </c>
     </row>
     <row r="61">
@@ -2664,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>51159562.05996025</v>
+        <v>51284750.60377108</v>
       </c>
       <c r="F61" t="n">
-        <v>51159562.05996025</v>
+        <v>51284750.60377108</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>51159562.05996025</v>
+        <v>51284750.60377108</v>
       </c>
     </row>
     <row r="62">
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-50327537.70444436</v>
+        <v>-48592513.46530405</v>
       </c>
       <c r="F62" t="n">
-        <v>-50327537.70444436</v>
+        <v>-48592513.46530405</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>-50327537.70444436</v>
+        <v>-48592513.46530405</v>
       </c>
     </row>
     <row r="63">
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1404698533.360361</v>
+        <v>1410236649.960449</v>
       </c>
       <c r="E63" t="n">
-        <v>397656888.5861675</v>
+        <v>396926332.4184159</v>
       </c>
       <c r="F63" t="n">
-        <v>1802355421.946528</v>
+        <v>1807162982.378865</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1802355421.946528</v>
+        <v>1807162982.378865</v>
       </c>
     </row>
     <row r="64">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4505195751.932012</v>
+        <v>4524110726.33026</v>
       </c>
       <c r="E64" t="n">
-        <v>1314111931.984749</v>
+        <v>1287150626.663693</v>
       </c>
       <c r="F64" t="n">
-        <v>5819307683.91676</v>
+        <v>5811261352.993954</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5819307683.91676</v>
+        <v>5811261352.993954</v>
       </c>
     </row>
   </sheetData>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-144251662.1232575</v>
+        <v>89322758.02045271</v>
       </c>
       <c r="C2" t="n">
-        <v>2233131347.127573</v>
+        <v>2046472793.945855</v>
       </c>
       <c r="D2" t="n">
-        <v>2088879685.004316</v>
+        <v>2135795551.966308</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-85376944.77949929</v>
+        <v>-56451590.73807764</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.114745398291608</v>
+        <v>-4.704299228173136</v>
       </c>
       <c r="H2" t="n">
-        <v>-85376944.77949929</v>
+        <v>-56451590.73807764</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.114745398291608</v>
+        <v>-4.704299228173136</v>
       </c>
     </row>
     <row r="3">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>475442510.2904696</v>
+        <v>612312108.7038262</v>
       </c>
       <c r="C3" t="n">
-        <v>1791770422.837109</v>
+        <v>1641340909.440661</v>
       </c>
       <c r="D3" t="n">
-        <v>2267212933.127579</v>
+        <v>2253653018.144486</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>92956303.34376431</v>
+        <v>61405875.44010115</v>
       </c>
       <c r="G3" t="n">
-        <v>7.746358611980359</v>
+        <v>5.117156286675096</v>
       </c>
       <c r="H3" t="n">
-        <v>46478151.67188215</v>
+        <v>30702937.72005057</v>
       </c>
       <c r="I3" t="n">
-        <v>3.873179305990179</v>
+        <v>2.558578143337548</v>
       </c>
     </row>
     <row r="4">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-8593058.749476984</v>
+        <v>207058195.6860675</v>
       </c>
       <c r="C4" t="n">
-        <v>2166960127.772038</v>
+        <v>1981277337.886086</v>
       </c>
       <c r="D4" t="n">
-        <v>2158367069.022562</v>
+        <v>2188335533.572155</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-15889560.76125336</v>
+        <v>-3911609.132230759</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.32413006343778</v>
+        <v>-0.3259674276858965</v>
       </c>
       <c r="H4" t="n">
-        <v>-15889560.76125336</v>
+        <v>-3911609.132230759</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.32413006343778</v>
+        <v>-0.3259674276858965</v>
       </c>
     </row>
     <row r="5">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>280961236.1696404</v>
+        <v>445155515.1194676</v>
       </c>
       <c r="C5" t="n">
-        <v>1900974766.689718</v>
+        <v>1745780284.034382</v>
       </c>
       <c r="D5" t="n">
-        <v>2181936002.859358</v>
+        <v>2190935799.15385</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7679373.075543404</v>
+        <v>-1311343.550535679</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6399477562952836</v>
+        <v>-0.1092786292113066</v>
       </c>
       <c r="H5" t="n">
-        <v>3839686.537771702</v>
+        <v>-1311343.550535679</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3199738781476418</v>
+        <v>-0.1092786292113066</v>
       </c>
     </row>
     <row r="6">
@@ -2980,13 +2980,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>139139834.0518155</v>
+        <v>325982926.7226974</v>
       </c>
       <c r="C6" t="n">
-        <v>2005960283.043716</v>
+        <v>1841325583.960047</v>
       </c>
       <c r="D6" t="n">
-        <v>2145100117.095532</v>
+        <v>2167308510.682744</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-29156512.68828297</v>
+        <v>-24938632.02164173</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.429709390690247</v>
+        <v>-2.078219335136811</v>
       </c>
       <c r="H6" t="n">
-        <v>-29156512.68828297</v>
+        <v>-24938632.02164173</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.429709390690247</v>
+        <v>-2.078219335136811</v>
       </c>
     </row>
     <row r="7">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>152845250.6160171</v>
+        <v>343412384.5888303</v>
       </c>
       <c r="C7" t="n">
-        <v>2051962750.690044</v>
+        <v>1875624874.005773</v>
       </c>
       <c r="D7" t="n">
-        <v>2204808001.306062</v>
+        <v>2219037258.594603</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3027,16 +3027,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>30551371.52224684</v>
+        <v>26790115.8902173</v>
       </c>
       <c r="G7" t="n">
-        <v>2.545947626853903</v>
+        <v>2.232509657518109</v>
       </c>
       <c r="H7" t="n">
-        <v>15275685.76112342</v>
+        <v>13395057.94510865</v>
       </c>
       <c r="I7" t="n">
-        <v>1.272973813426952</v>
+        <v>1.116254828759054</v>
       </c>
     </row>
     <row r="8">
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>272705502.6861358</v>
+        <v>441561505.4877738</v>
       </c>
       <c r="C8" t="n">
-        <v>1938224649.46354</v>
+        <v>1775412148.751081</v>
       </c>
       <c r="D8" t="n">
-        <v>2210930152.149676</v>
+        <v>2216973654.238855</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>36673522.36586094</v>
+        <v>24726511.53447008</v>
       </c>
       <c r="G8" t="n">
-        <v>3.056126863821745</v>
+        <v>2.060542627872507</v>
       </c>
       <c r="H8" t="n">
-        <v>18336761.18293047</v>
+        <v>12363255.76723504</v>
       </c>
       <c r="I8" t="n">
-        <v>1.528063431910873</v>
+        <v>1.030271313936253</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/eve_results.xlsx
+++ b/irrbb_calc/output/eve_results.xlsx
@@ -458,13 +458,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-6888942153.225</v>
+        <v>-6979096005.9545</v>
       </c>
       <c r="D2" t="n">
-        <v>-95574548.38871074</v>
+        <v>-65780582.74599808</v>
       </c>
       <c r="E2" t="n">
-        <v>-6984516701.61371</v>
+        <v>-7044876588.700498</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1462419213.865</v>
+        <v>1307956101.245</v>
       </c>
       <c r="D3" t="n">
-        <v>172538778.3262466</v>
+        <v>189967292.1020061</v>
       </c>
       <c r="E3" t="n">
-        <v>1634957992.191247</v>
+        <v>1497923393.347006</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +503,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-6667024.314525582</v>
+        <v>7893527.93842428</v>
       </c>
       <c r="E4" t="n">
-        <v>-6667024.314525582</v>
+        <v>7893527.93842428</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5761171342.164854</v>
+        <v>5914737978.28509</v>
       </c>
       <c r="D5" t="n">
-        <v>1787301534.276521</v>
+        <v>1632785001.551335</v>
       </c>
       <c r="E5" t="n">
-        <v>7548472876.441375</v>
+        <v>7547522979.836426</v>
       </c>
     </row>
   </sheetData>
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>334648402.8048539</v>
+        <v>243598073.5755906</v>
       </c>
       <c r="C2" t="n">
-        <v>1857598739.899531</v>
+        <v>1764865238.845767</v>
       </c>
       <c r="D2" t="n">
-        <v>2192247142.704385</v>
+        <v>2008463312.421358</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3266226781.875385</v>
+        <v>-3343000690.496193</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-3266226781.875385</v>
+        <v>-3343000690.496193</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-3266226781.875385</v>
+        <v>-3343000690.496193</v>
       </c>
     </row>
     <row r="3">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1763101306.462626</v>
+        <v>-1742776934.318</v>
       </c>
       <c r="E3" t="n">
-        <v>-21149120.47938829</v>
+        <v>-15293479.54218755</v>
       </c>
       <c r="F3" t="n">
-        <v>-1784250426.942014</v>
+        <v>-1758070413.860187</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1784250426.942014</v>
+        <v>-1758070413.860187</v>
       </c>
     </row>
     <row r="4">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1644897139.926168</v>
+        <v>-1668807372.95979</v>
       </c>
       <c r="E4" t="n">
-        <v>-102095128.5477959</v>
+        <v>-79479728.27594785</v>
       </c>
       <c r="F4" t="n">
-        <v>-1746992268.473964</v>
+        <v>-1748287101.235738</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-1746992268.473964</v>
+        <v>-1748287101.235738</v>
       </c>
     </row>
     <row r="5">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1034037645.955366</v>
+        <v>1264322069.253984</v>
       </c>
       <c r="E5" t="n">
-        <v>147970901.3942873</v>
+        <v>203210087.9608278</v>
       </c>
       <c r="F5" t="n">
-        <v>1182008547.349654</v>
+        <v>1467532157.214812</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1182008547.349654</v>
+        <v>1467532157.214812</v>
       </c>
     </row>
     <row r="6">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>369225148.204857</v>
+        <v>-31115057.81660692</v>
       </c>
       <c r="E6" t="n">
-        <v>25234324.21323526</v>
+        <v>-34104151.55555091</v>
       </c>
       <c r="F6" t="n">
-        <v>394459472.4180922</v>
+        <v>-65219209.37215786</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>394459472.4180922</v>
+        <v>-65219209.37215786</v>
       </c>
     </row>
     <row r="7">
@@ -828,10 +828,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>48510363.61575694</v>
+        <v>49528534.24319372</v>
       </c>
       <c r="F7" t="n">
-        <v>48510363.61575694</v>
+        <v>49528534.24319372</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>48510363.61575694</v>
+        <v>49528534.24319372</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-77437894.22171178</v>
+        <v>-64731775.20208906</v>
       </c>
       <c r="F8" t="n">
-        <v>-77437894.22171178</v>
+        <v>-64731775.20208906</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-77437894.22171178</v>
+        <v>-64731775.20208906</v>
       </c>
     </row>
     <row r="9">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1290284599.41296</v>
+        <v>1569682088.991834</v>
       </c>
       <c r="E9" t="n">
-        <v>371091066.5848168</v>
+        <v>428435111.1367694</v>
       </c>
       <c r="F9" t="n">
-        <v>1661375665.997777</v>
+        <v>1998117200.128603</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1661375665.997777</v>
+        <v>1998117200.128603</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4070000592.711449</v>
+        <v>3909576816.560989</v>
       </c>
       <c r="E10" t="n">
-        <v>1654348281.386654</v>
+        <v>1453758701.572267</v>
       </c>
       <c r="F10" t="n">
-        <v>5724348874.098104</v>
+        <v>5363335518.133256</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5724348874.098104</v>
+        <v>5363335518.133256</v>
       </c>
     </row>
     <row r="11">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3595018797.100747</v>
+        <v>-3689248189.734171</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-3595018797.100747</v>
+        <v>-3689248189.734171</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3595018797.100747</v>
+        <v>-3689248189.734171</v>
       </c>
     </row>
     <row r="12">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1785303105.702563</v>
+        <v>-1765345101.208171</v>
       </c>
       <c r="E12" t="n">
-        <v>-21503393.44474231</v>
+        <v>-15556314.46025577</v>
       </c>
       <c r="F12" t="n">
-        <v>-1806806499.147305</v>
+        <v>-1780901415.668427</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-1806806499.147305</v>
+        <v>-1780901415.668427</v>
       </c>
     </row>
     <row r="13">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1742750122.204495</v>
+        <v>-1769548625.88353</v>
       </c>
       <c r="E13" t="n">
-        <v>-45009890.26630468</v>
+        <v>-19486412.52932518</v>
       </c>
       <c r="F13" t="n">
-        <v>-1787760012.470799</v>
+        <v>-1789035038.412855</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-1787760012.470799</v>
+        <v>-1789035038.412855</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1137390921.40021</v>
+        <v>1449103309.931738</v>
       </c>
       <c r="E14" t="n">
-        <v>162957026.400852</v>
+        <v>223933448.173169</v>
       </c>
       <c r="F14" t="n">
-        <v>1300347947.801062</v>
+        <v>1673036758.104907</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1300347947.801062</v>
+        <v>1673036758.104907</v>
       </c>
     </row>
     <row r="15">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>388839345.5165195</v>
+        <v>-60138220.01168863</v>
       </c>
       <c r="E15" t="n">
-        <v>9517205.231710548</v>
+        <v>-10276900.48654187</v>
       </c>
       <c r="F15" t="n">
-        <v>398356550.74823</v>
+        <v>-70415120.49823055</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>398356550.74823</v>
+        <v>-70415120.49823055</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>52535642.07256661</v>
+        <v>53660693.14639333</v>
       </c>
       <c r="F16" t="n">
-        <v>52535642.07256661</v>
+        <v>53660693.14639333</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>52535642.07256661</v>
+        <v>53660693.14639333</v>
       </c>
     </row>
     <row r="17">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-35309118.0728855</v>
+        <v>-20988330.63837767</v>
       </c>
       <c r="F17" t="n">
-        <v>-35309118.0728855</v>
+        <v>-20988330.63837767</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-35309118.0728855</v>
+        <v>-20988330.63837767</v>
       </c>
     </row>
     <row r="18">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1466801922.604962</v>
+        <v>1797519713.843014</v>
       </c>
       <c r="E18" t="n">
-        <v>408885959.6564559</v>
+        <v>473821545.457775</v>
       </c>
       <c r="F18" t="n">
-        <v>1875687882.261418</v>
+        <v>2271341259.300789</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1875687882.261418</v>
+        <v>2271341259.300789</v>
       </c>
     </row>
     <row r="19">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4742351944.18994</v>
+        <v>4608249797.671778</v>
       </c>
       <c r="E19" t="n">
-        <v>1109267477.863008</v>
+        <v>872645836.627254</v>
       </c>
       <c r="F19" t="n">
-        <v>5851619422.052948</v>
+        <v>5480895634.299032</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5851619422.052948</v>
+        <v>5480895634.299032</v>
       </c>
     </row>
     <row r="20">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3350370224.440778</v>
+        <v>-3431022674.68616</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-3350370224.440778</v>
+        <v>-3431022674.68616</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-3350370224.440778</v>
+        <v>-3431022674.68616</v>
       </c>
     </row>
     <row r="21">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1779746658.917952</v>
+        <v>-1759613838.779673</v>
       </c>
       <c r="E21" t="n">
-        <v>-21406898.03703971</v>
+        <v>-15483841.00286351</v>
       </c>
       <c r="F21" t="n">
-        <v>-1801153556.954991</v>
+        <v>-1775097679.782537</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-1801153556.954991</v>
+        <v>-1775097679.782537</v>
       </c>
     </row>
     <row r="22">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1677629089.713623</v>
+        <v>-1702312063.613388</v>
       </c>
       <c r="E22" t="n">
-        <v>-83224804.8379025</v>
+        <v>-59764962.08873813</v>
       </c>
       <c r="F22" t="n">
-        <v>-1760853894.551526</v>
+        <v>-1762077025.702126</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>-1760853894.551526</v>
+        <v>-1762077025.702126</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1061099376.039827</v>
+        <v>1310247452.871499</v>
       </c>
       <c r="E23" t="n">
-        <v>152607174.9130457</v>
+        <v>209474717.2358064</v>
       </c>
       <c r="F23" t="n">
-        <v>1213706550.952873</v>
+        <v>1519722170.107305</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1213706550.952873</v>
+        <v>1519722170.107305</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>378103073.8886718</v>
+        <v>-35646133.80847277</v>
       </c>
       <c r="E24" t="n">
-        <v>19660348.80291696</v>
+        <v>-32583946.50832415</v>
       </c>
       <c r="F24" t="n">
-        <v>397763422.6915888</v>
+        <v>-68230080.31679693</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>397763422.6915888</v>
+        <v>-68230080.31679693</v>
       </c>
     </row>
     <row r="25">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>49898248.72997621</v>
+        <v>50949246.19788411</v>
       </c>
       <c r="F25" t="n">
-        <v>49898248.72997621</v>
+        <v>50949246.19788411</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>49898248.72997621</v>
+        <v>50949246.19788411</v>
       </c>
     </row>
     <row r="26">
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-68401471.02437343</v>
+        <v>-55240771.49147542</v>
       </c>
       <c r="F26" t="n">
-        <v>-68401471.02437343</v>
+        <v>-55240771.49147542</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-68401471.02437343</v>
+        <v>-55240771.49147542</v>
       </c>
     </row>
     <row r="27">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1337385594.490246</v>
+        <v>1629207873.275736</v>
       </c>
       <c r="E27" t="n">
-        <v>382430248.7819011</v>
+        <v>441838934.0193523</v>
       </c>
       <c r="F27" t="n">
-        <v>1719815843.272147</v>
+        <v>2071046807.295089</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1719815843.272147</v>
+        <v>2071046807.295089</v>
       </c>
     </row>
     <row r="28">
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4238216124.339675</v>
+        <v>4079964199.723892</v>
       </c>
       <c r="E28" t="n">
-        <v>1549714490.557562</v>
+        <v>1339021267.737889</v>
       </c>
       <c r="F28" t="n">
-        <v>5787930614.897237</v>
+        <v>5418985467.461781</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5787930614.897237</v>
+        <v>5418985467.461781</v>
       </c>
     </row>
     <row r="29">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-3481869103.010223</v>
+        <v>-3570626119.017644</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-3481869103.010223</v>
+        <v>-3570626119.017644</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-3481869103.010223</v>
+        <v>-3570626119.017644</v>
       </c>
     </row>
     <row r="30">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1766637513.292219</v>
+        <v>-1746459477.633495</v>
       </c>
       <c r="E30" t="n">
-        <v>-21213840.11837501</v>
+        <v>-15342428.22534983</v>
       </c>
       <c r="F30" t="n">
-        <v>-1787851353.410594</v>
+        <v>-1761801905.858845</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-1787851353.410594</v>
+        <v>-1761801905.858845</v>
       </c>
     </row>
     <row r="31">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-1702352079.45932</v>
+        <v>-1728154165.056717</v>
       </c>
       <c r="E31" t="n">
-        <v>-67934398.36046064</v>
+        <v>-43890063.38454545</v>
       </c>
       <c r="F31" t="n">
-        <v>-1770286477.819781</v>
+        <v>-1772044228.441262</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1770286477.819781</v>
+        <v>-1772044228.441262</v>
       </c>
     </row>
     <row r="32">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1101677534.406734</v>
+        <v>1387666416.822766</v>
       </c>
       <c r="E32" t="n">
-        <v>157104719.9201794</v>
+        <v>215993235.0308178</v>
       </c>
       <c r="F32" t="n">
-        <v>1258782254.326914</v>
+        <v>1603659651.853584</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1258782254.326914</v>
+        <v>1603659651.853584</v>
       </c>
     </row>
     <row r="33">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>378478669.4771072</v>
+        <v>-52851220.97648965</v>
       </c>
       <c r="E33" t="n">
-        <v>16197755.8063393</v>
+        <v>-14126926.9717582</v>
       </c>
       <c r="F33" t="n">
-        <v>394676425.2834465</v>
+        <v>-66978147.94824776</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>394676425.2834465</v>
+        <v>-66978147.94824776</v>
       </c>
     </row>
     <row r="34">
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>50834746.09217594</v>
+        <v>51918672.77361196</v>
       </c>
       <c r="F34" t="n">
-        <v>50834746.09217594</v>
+        <v>51918672.77361196</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>50834746.09217594</v>
+        <v>51918672.77361196</v>
       </c>
     </row>
     <row r="35">
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-47533029.96106433</v>
+        <v>-33793464.28046042</v>
       </c>
       <c r="F35" t="n">
-        <v>-47533029.96106433</v>
+        <v>-33793464.28046042</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-47533029.96106433</v>
+        <v>-33793464.28046042</v>
       </c>
     </row>
     <row r="36">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1404286294.030221</v>
+        <v>1717870607.287968</v>
       </c>
       <c r="E36" t="n">
-        <v>394398573.8916682</v>
+        <v>456617144.5540742</v>
       </c>
       <c r="F36" t="n">
-        <v>1798684867.92189</v>
+        <v>2174487751.842042</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1798684867.92189</v>
+        <v>2174487751.842042</v>
       </c>
     </row>
     <row r="37">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4511571712.967167</v>
+        <v>4370186303.292678</v>
       </c>
       <c r="E37" t="n">
-        <v>1263925756.763919</v>
+        <v>1043231633.793297</v>
       </c>
       <c r="F37" t="n">
-        <v>5775497469.731086</v>
+        <v>5413417937.085975</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5775497469.731086</v>
+        <v>5413417937.085975</v>
       </c>
     </row>
     <row r="38">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-3408319333.568017</v>
+        <v>-3493089952.872704</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-3408319333.568017</v>
+        <v>-3493089952.872704</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-3408319333.568017</v>
+        <v>-3493089952.872704</v>
       </c>
     </row>
     <row r="39">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1763023548.783077</v>
+        <v>-1742776623.671723</v>
       </c>
       <c r="E39" t="n">
-        <v>-21155303.92068019</v>
+        <v>-15298901.92016511</v>
       </c>
       <c r="F39" t="n">
-        <v>-1784178852.703757</v>
+        <v>-1758075525.591888</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-1784178852.703757</v>
+        <v>-1758075525.591888</v>
       </c>
     </row>
     <row r="40">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1681589662.459445</v>
+        <v>-1706754645.599518</v>
       </c>
       <c r="E40" t="n">
-        <v>-80183693.33477247</v>
+        <v>-56661569.98618495</v>
       </c>
       <c r="F40" t="n">
-        <v>-1761773355.794217</v>
+        <v>-1763416215.585703</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>-1761773355.794217</v>
+        <v>-1763416215.585703</v>
       </c>
     </row>
     <row r="41">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1078701226.475918</v>
+        <v>1346232393.261463</v>
       </c>
       <c r="E41" t="n">
-        <v>153870138.305684</v>
+        <v>211501179.4371307</v>
       </c>
       <c r="F41" t="n">
-        <v>1232571364.781602</v>
+        <v>1557733572.698594</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1232571364.781602</v>
+        <v>1557733572.698594</v>
       </c>
     </row>
     <row r="42">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>374636825.6386479</v>
+        <v>-45921221.17908719</v>
       </c>
       <c r="E42" t="n">
-        <v>19447147.64639056</v>
+        <v>-20112574.33891214</v>
       </c>
       <c r="F42" t="n">
-        <v>394083973.2850384</v>
+        <v>-66033795.5179993</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>394083973.2850384</v>
+        <v>-66033795.5179993</v>
       </c>
     </row>
     <row r="43">
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>49986696.06493255</v>
+        <v>51047586.25519484</v>
       </c>
       <c r="F43" t="n">
-        <v>49986696.06493255</v>
+        <v>51047586.25519484</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>49986696.06493255</v>
+        <v>51047586.25519484</v>
       </c>
     </row>
     <row r="44">
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-57093505.77639623</v>
+        <v>-43707800.03966388</v>
       </c>
       <c r="F44" t="n">
-        <v>-57093505.77639623</v>
+        <v>-43707800.03966388</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-57093505.77639623</v>
+        <v>-43707800.03966388</v>
       </c>
     </row>
     <row r="45">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1365082572.829281</v>
+        <v>1667080655.739377</v>
       </c>
       <c r="E45" t="n">
-        <v>386183837.0818647</v>
+        <v>446722472.4544179</v>
       </c>
       <c r="F45" t="n">
-        <v>1751266409.911145</v>
+        <v>2113803128.193795</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1751266409.911145</v>
+        <v>2113803128.193795</v>
       </c>
     </row>
     <row r="46">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4360494846.589389</v>
+        <v>4212433738.29099</v>
       </c>
       <c r="E46" t="n">
-        <v>1390270267.893024</v>
+        <v>1177744043.618858</v>
       </c>
       <c r="F46" t="n">
-        <v>5750765114.482412</v>
+        <v>5390177781.909848</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5750765114.482412</v>
+        <v>5390177781.909848</v>
       </c>
     </row>
     <row r="47">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3436422167.635112</v>
+        <v>-3521631895.511834</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-3436422167.635112</v>
+        <v>-3521631895.511834</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-3436422167.635112</v>
+        <v>-3521631895.511834</v>
       </c>
     </row>
     <row r="48">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1785375225.87358</v>
+        <v>-1765338338.610486</v>
       </c>
       <c r="E48" t="n">
-        <v>-21497026.15281431</v>
+        <v>-15550741.29227038</v>
       </c>
       <c r="F48" t="n">
-        <v>-1806872252.026394</v>
+        <v>-1780889079.902756</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>-1806872252.026394</v>
+        <v>-1780889079.902756</v>
       </c>
     </row>
     <row r="49">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1703472255.03539</v>
+        <v>-1728920322.026629</v>
       </c>
       <c r="E49" t="n">
-        <v>-68022275.66406374</v>
+        <v>-43910420.05504028</v>
       </c>
       <c r="F49" t="n">
-        <v>-1771494530.699454</v>
+        <v>-1772830742.08167</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1771494530.699454</v>
+        <v>-1772830742.08167</v>
       </c>
     </row>
     <row r="50">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1088289858.372025</v>
+        <v>1358832326.732567</v>
       </c>
       <c r="E50" t="n">
-        <v>156555015.3044434</v>
+        <v>214935859.3762352</v>
       </c>
       <c r="F50" t="n">
-        <v>1244844873.676469</v>
+        <v>1573768186.108802</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1244844873.676469</v>
+        <v>1573768186.108802</v>
       </c>
     </row>
     <row r="51">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>383294129.9808388</v>
+        <v>-43167099.5280119</v>
       </c>
       <c r="E51" t="n">
-        <v>15441583.74985308</v>
+        <v>-26414108.66164763</v>
       </c>
       <c r="F51" t="n">
-        <v>398735713.7306919</v>
+        <v>-69581208.18965958</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>398735713.7306919</v>
+        <v>-69581208.18965958</v>
       </c>
     </row>
     <row r="52">
@@ -2358,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>50962119.71324782</v>
+        <v>52041402.59864988</v>
       </c>
       <c r="F52" t="n">
-        <v>50962119.71324782</v>
+        <v>52041402.59864988</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>50962119.71324782</v>
+        <v>52041402.59864988</v>
       </c>
     </row>
     <row r="53">
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>-57176662.31307409</v>
+        <v>-43588973.21809262</v>
       </c>
       <c r="F53" t="n">
-        <v>-57176662.31307409</v>
+        <v>-43588973.21809262</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-57176662.31307409</v>
+        <v>-43588973.21809262</v>
       </c>
     </row>
     <row r="54">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1383628247.441011</v>
+        <v>1688842744.04984</v>
       </c>
       <c r="E54" t="n">
-        <v>392363944.1245303</v>
+        <v>453763954.7393798</v>
       </c>
       <c r="F54" t="n">
-        <v>1775992191.565542</v>
+        <v>2142606698.789219</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1775992191.565542</v>
+        <v>2142606698.789219</v>
       </c>
     </row>
     <row r="55">
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4413469797.339037</v>
+        <v>4261447978.416411</v>
       </c>
       <c r="E55" t="n">
-        <v>1406998175.24365</v>
+        <v>1187583015.60945</v>
       </c>
       <c r="F55" t="n">
-        <v>5820467972.582687</v>
+        <v>5449030994.025861</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5820467972.582687</v>
+        <v>5449030994.025861</v>
       </c>
     </row>
     <row r="56">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-3489288375.749453</v>
+        <v>-3577843923.188877</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-3489288375.749453</v>
+        <v>-3577843923.188877</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>-3489288375.749453</v>
+        <v>-3577843923.188877</v>
       </c>
     </row>
     <row r="57">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1778603733.837346</v>
+        <v>-1758534376.095333</v>
       </c>
       <c r="E57" t="n">
-        <v>-21396414.2172313</v>
+        <v>-15476937.61869058</v>
       </c>
       <c r="F57" t="n">
-        <v>-1800000148.054577</v>
+        <v>-1774011313.714024</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>-1800000148.054577</v>
+        <v>-1774011313.714024</v>
       </c>
     </row>
     <row r="58">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1712254318.096915</v>
+        <v>-1738145377.778625</v>
       </c>
       <c r="E58" t="n">
-        <v>-62506711.91301568</v>
+        <v>-38192330.92807065</v>
       </c>
       <c r="F58" t="n">
-        <v>-1774761030.009931</v>
+        <v>-1776337708.706696</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>-1774761030.009931</v>
+        <v>-1776337708.706696</v>
       </c>
     </row>
     <row r="59">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1104480703.024926</v>
+        <v>1390090199.843369</v>
       </c>
       <c r="E59" t="n">
-        <v>158241827.4283697</v>
+        <v>217409195.1515212</v>
       </c>
       <c r="F59" t="n">
-        <v>1262722530.453295</v>
+        <v>1607499394.994891</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1262722530.453295</v>
+        <v>1607499394.994891</v>
       </c>
     </row>
     <row r="60">
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>382879853.8558538</v>
+        <v>-50514098.88786048</v>
       </c>
       <c r="E60" t="n">
-        <v>14304251.23238228</v>
+        <v>-18323108.1958431</v>
       </c>
       <c r="F60" t="n">
-        <v>397184105.088236</v>
+        <v>-68837207.08370358</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>397184105.088236</v>
+        <v>-68837207.08370358</v>
       </c>
     </row>
     <row r="61">
@@ -2664,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>51284750.60377108</v>
+        <v>52376409.34303474</v>
       </c>
       <c r="F61" t="n">
-        <v>51284750.60377108</v>
+        <v>52376409.34303474</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>51284750.60377108</v>
+        <v>52376409.34303474</v>
       </c>
     </row>
     <row r="62">
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-48592513.46530405</v>
+        <v>-34779061.88385776</v>
       </c>
       <c r="F62" t="n">
-        <v>-48592513.46530405</v>
+        <v>-34779061.88385776</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>-48592513.46530405</v>
+        <v>-34779061.88385776</v>
       </c>
     </row>
     <row r="63">
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1410236649.960449</v>
+        <v>1724311624.301515</v>
       </c>
       <c r="E63" t="n">
-        <v>396926332.4184159</v>
+        <v>459437379.7355413</v>
       </c>
       <c r="F63" t="n">
-        <v>1807162982.378865</v>
+        <v>2183749004.037056</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1807162982.378865</v>
+        <v>2183749004.037056</v>
       </c>
     </row>
     <row r="64">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4524110726.33026</v>
+        <v>4379700742.660229</v>
       </c>
       <c r="E64" t="n">
-        <v>1287150626.663693</v>
+        <v>1063636123.353978</v>
       </c>
       <c r="F64" t="n">
-        <v>5811261352.993954</v>
+        <v>5443336866.014207</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5811261352.993954</v>
+        <v>5443336866.014207</v>
       </c>
     </row>
   </sheetData>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89322758.02045271</v>
+        <v>-42119080.78378276</v>
       </c>
       <c r="C2" t="n">
-        <v>2046472793.945855</v>
+        <v>1941323300.337283</v>
       </c>
       <c r="D2" t="n">
-        <v>2135795551.966308</v>
+        <v>1899204219.5535</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-56451590.73807764</v>
+        <v>-109259092.8678579</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.704299228173136</v>
+        <v>-9.104924405654828</v>
       </c>
       <c r="H2" t="n">
-        <v>-56451590.73807764</v>
+        <v>-109259092.8678579</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.704299228173136</v>
+        <v>-9.104924405654828</v>
       </c>
     </row>
     <row r="3">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>612312108.7038262</v>
+        <v>570592684.6089693</v>
       </c>
       <c r="C3" t="n">
-        <v>1641340909.440661</v>
+        <v>1557753565.290091</v>
       </c>
       <c r="D3" t="n">
-        <v>2253653018.144486</v>
+        <v>2128346249.89906</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>61405875.44010115</v>
+        <v>119882937.4777024</v>
       </c>
       <c r="G3" t="n">
-        <v>5.117156286675096</v>
+        <v>9.990244789808532</v>
       </c>
       <c r="H3" t="n">
-        <v>30702937.72005057</v>
+        <v>59941468.73885119</v>
       </c>
       <c r="I3" t="n">
-        <v>2.558578143337548</v>
+        <v>4.995122394904266</v>
       </c>
     </row>
     <row r="4">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>207058195.6860675</v>
+        <v>90824814.98343299</v>
       </c>
       <c r="C4" t="n">
-        <v>1981277337.886086</v>
+        <v>1878210644.09953</v>
       </c>
       <c r="D4" t="n">
-        <v>2188335533.572155</v>
+        <v>1969035459.082963</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-3911609.132230759</v>
+        <v>-39427853.33839488</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3259674276858965</v>
+        <v>-3.28565444486624</v>
       </c>
       <c r="H4" t="n">
-        <v>-3911609.132230759</v>
+        <v>-39427853.33839488</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3259674276858965</v>
+        <v>-3.28565444486624</v>
       </c>
     </row>
     <row r="5">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>445155515.1194676</v>
+        <v>377632344.7190661</v>
       </c>
       <c r="C5" t="n">
-        <v>1745780284.034382</v>
+        <v>1660607803.289687</v>
       </c>
       <c r="D5" t="n">
-        <v>2190935799.15385</v>
+        <v>2038240148.008754</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-1311343.550535679</v>
+        <v>29776835.58739567</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1092786292113066</v>
+        <v>2.481402965616306</v>
       </c>
       <c r="H5" t="n">
-        <v>-1311343.550535679</v>
+        <v>14888417.79369783</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1092786292113066</v>
+        <v>1.240701482808153</v>
       </c>
     </row>
     <row r="6">
@@ -2980,13 +2980,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>325982926.7226974</v>
+        <v>237204343.9687985</v>
       </c>
       <c r="C6" t="n">
-        <v>1841325583.960047</v>
+        <v>1751234435.480675</v>
       </c>
       <c r="D6" t="n">
-        <v>2167308510.682744</v>
+        <v>1988438779.449474</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-24938632.02164173</v>
+        <v>-20024532.97188425</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.078219335136811</v>
+        <v>-1.668711080990354</v>
       </c>
       <c r="H6" t="n">
-        <v>-24938632.02164173</v>
+        <v>-20024532.97188425</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.078219335136811</v>
+        <v>-1.668711080990354</v>
       </c>
     </row>
     <row r="7">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>343412384.5888303</v>
+        <v>250065393.5218567</v>
       </c>
       <c r="C7" t="n">
-        <v>1875624874.005773</v>
+        <v>1778859989.096664</v>
       </c>
       <c r="D7" t="n">
-        <v>2219037258.594603</v>
+        <v>2028925382.61852</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3027,16 +3027,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>26790115.8902173</v>
+        <v>20462070.19716263</v>
       </c>
       <c r="G7" t="n">
-        <v>2.232509657518109</v>
+        <v>1.705172516430219</v>
       </c>
       <c r="H7" t="n">
-        <v>13395057.94510865</v>
+        <v>10231035.09858131</v>
       </c>
       <c r="I7" t="n">
-        <v>1.116254828759054</v>
+        <v>0.8525862582151095</v>
       </c>
     </row>
     <row r="8">
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>441561505.4877738</v>
+        <v>369064790.8544175</v>
       </c>
       <c r="C8" t="n">
-        <v>1775412148.751081</v>
+        <v>1686087668.957613</v>
       </c>
       <c r="D8" t="n">
-        <v>2216973654.238855</v>
+        <v>2055152459.812031</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24726511.53447008</v>
+        <v>46689147.39067268</v>
       </c>
       <c r="G8" t="n">
-        <v>2.060542627872507</v>
+        <v>3.890762282556057</v>
       </c>
       <c r="H8" t="n">
-        <v>12363255.76723504</v>
+        <v>23344573.69533634</v>
       </c>
       <c r="I8" t="n">
-        <v>1.030271313936253</v>
+        <v>1.945381141278028</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/eve_results.xlsx
+++ b/irrbb_calc/output/eve_results.xlsx
@@ -458,13 +458,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-6979096005.9545</v>
+        <v>-6998259864.5985</v>
       </c>
       <c r="D2" t="n">
-        <v>-65780582.74599808</v>
+        <v>-68194981.27489617</v>
       </c>
       <c r="E2" t="n">
-        <v>-7044876588.700498</v>
+        <v>-7066454845.873396</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1307956101.245</v>
+        <v>1393570295.485</v>
       </c>
       <c r="D3" t="n">
-        <v>189967292.1020061</v>
+        <v>198799202.163694</v>
       </c>
       <c r="E3" t="n">
-        <v>1497923393.347006</v>
+        <v>1592369497.648694</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +503,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>7893527.93842428</v>
+        <v>11994549.74919581</v>
       </c>
       <c r="E4" t="n">
-        <v>7893527.93842428</v>
+        <v>11994549.74919581</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5914737978.28509</v>
+        <v>5909094452.606114</v>
       </c>
       <c r="D5" t="n">
-        <v>1632785001.551335</v>
+        <v>1647994692.620192</v>
       </c>
       <c r="E5" t="n">
-        <v>7547522979.836426</v>
+        <v>7557089145.226307</v>
       </c>
     </row>
   </sheetData>
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>243598073.5755906</v>
+        <v>304404883.4926145</v>
       </c>
       <c r="C2" t="n">
-        <v>1764865238.845767</v>
+        <v>1790593463.258186</v>
       </c>
       <c r="D2" t="n">
-        <v>2008463312.421358</v>
+        <v>2094998346.7508</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3343000690.496193</v>
+        <v>-3083318426.864177</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-3343000690.496193</v>
+        <v>-3083318426.864177</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-3343000690.496193</v>
+        <v>-3083318426.864177</v>
       </c>
     </row>
     <row r="3">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1742776934.318</v>
+        <v>-2034037268.568554</v>
       </c>
       <c r="E3" t="n">
-        <v>-15293479.54218755</v>
+        <v>-17871399.19932215</v>
       </c>
       <c r="F3" t="n">
-        <v>-1758070413.860187</v>
+        <v>-2051908667.767876</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1758070413.860187</v>
+        <v>-2051908667.767876</v>
       </c>
     </row>
     <row r="4">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1668807372.95979</v>
+        <v>-1669116692.975606</v>
       </c>
       <c r="E4" t="n">
-        <v>-79479728.27594785</v>
+        <v>-79293869.85289092</v>
       </c>
       <c r="F4" t="n">
-        <v>-1748287101.235738</v>
+        <v>-1748410562.828497</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-1748287101.235738</v>
+        <v>-1748410562.828497</v>
       </c>
     </row>
     <row r="5">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1264322069.253984</v>
+        <v>1411203277.642081</v>
       </c>
       <c r="E5" t="n">
-        <v>203210087.9608278</v>
+        <v>188452797.5779153</v>
       </c>
       <c r="F5" t="n">
-        <v>1467532157.214812</v>
+        <v>1599656075.219997</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1467532157.214812</v>
+        <v>1599656075.219997</v>
       </c>
     </row>
     <row r="6">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-31115057.81660692</v>
+        <v>-99995931.64958692</v>
       </c>
       <c r="E6" t="n">
-        <v>-34104151.55555091</v>
+        <v>4633135.088666648</v>
       </c>
       <c r="F6" t="n">
-        <v>-65219209.37215786</v>
+        <v>-95362796.56092025</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-65219209.37215786</v>
+        <v>-95362796.56092025</v>
       </c>
     </row>
     <row r="7">
@@ -828,10 +828,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>49528534.24319372</v>
+        <v>64466094.07610536</v>
       </c>
       <c r="F7" t="n">
-        <v>49528534.24319372</v>
+        <v>64466094.07610536</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>49528534.24319372</v>
+        <v>64466094.07610536</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-64731775.20208906</v>
+        <v>-81272491.44740647</v>
       </c>
       <c r="F8" t="n">
-        <v>-64731775.20208906</v>
+        <v>-81272491.44740647</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-64731775.20208906</v>
+        <v>-81272491.44740647</v>
       </c>
     </row>
     <row r="9">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1569682088.991834</v>
+        <v>1569088185.802197</v>
       </c>
       <c r="E9" t="n">
-        <v>428435111.1367694</v>
+        <v>432174707.4322792</v>
       </c>
       <c r="F9" t="n">
-        <v>1998117200.128603</v>
+        <v>2001262893.234477</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1998117200.128603</v>
+        <v>2001262893.234477</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3909576816.560989</v>
+        <v>3900141505.855082</v>
       </c>
       <c r="E10" t="n">
-        <v>1453758701.572267</v>
+        <v>1467782727.012771</v>
       </c>
       <c r="F10" t="n">
-        <v>5363335518.133256</v>
+        <v>5367924232.867853</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5363335518.133256</v>
+        <v>5367924232.867853</v>
       </c>
     </row>
     <row r="11">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3689248189.734171</v>
+        <v>-3399019507.228214</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-3689248189.734171</v>
+        <v>-3399019507.228214</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3689248189.734171</v>
+        <v>-3399019507.228214</v>
       </c>
     </row>
     <row r="12">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1765345101.208171</v>
+        <v>-2060409643.124485</v>
       </c>
       <c r="E12" t="n">
-        <v>-15556314.46025577</v>
+        <v>-18179497.72119847</v>
       </c>
       <c r="F12" t="n">
-        <v>-1780901415.668427</v>
+        <v>-2078589140.845684</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-1780901415.668427</v>
+        <v>-2078589140.845684</v>
       </c>
     </row>
     <row r="13">
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1769548625.88353</v>
+        <v>-1769612025.91715</v>
       </c>
       <c r="E13" t="n">
-        <v>-19486412.52932518</v>
+        <v>-19300184.74962382</v>
       </c>
       <c r="F13" t="n">
-        <v>-1789035038.412855</v>
+        <v>-1788912210.666773</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-1789035038.412855</v>
+        <v>-1788912210.666773</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1449103309.931738</v>
+        <v>1584543845.963547</v>
       </c>
       <c r="E14" t="n">
-        <v>223933448.173169</v>
+        <v>207018836.9538093</v>
       </c>
       <c r="F14" t="n">
-        <v>1673036758.104907</v>
+        <v>1791562682.917356</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1673036758.104907</v>
+        <v>1791562682.917356</v>
       </c>
     </row>
     <row r="15">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-60138220.01168863</v>
+        <v>-100233118.0900111</v>
       </c>
       <c r="E15" t="n">
-        <v>-10276900.48654187</v>
+        <v>-2270936.089947926</v>
       </c>
       <c r="F15" t="n">
-        <v>-70415120.49823055</v>
+        <v>-102504054.179959</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-70415120.49823055</v>
+        <v>-102504054.179959</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>53660693.14639333</v>
+        <v>69575555.98605023</v>
       </c>
       <c r="F16" t="n">
-        <v>53660693.14639333</v>
+        <v>69575555.98605023</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>53660693.14639333</v>
+        <v>69575555.98605023</v>
       </c>
     </row>
     <row r="17">
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-20988330.63837767</v>
+        <v>-26721643.97585558</v>
       </c>
       <c r="F17" t="n">
-        <v>-20988330.63837767</v>
+        <v>-26721643.97585558</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-20988330.63837767</v>
+        <v>-26721643.97585558</v>
       </c>
     </row>
     <row r="18">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1797519713.843014</v>
+        <v>1798403894.897735</v>
       </c>
       <c r="E18" t="n">
-        <v>473821545.457775</v>
+        <v>478121492.5672495</v>
       </c>
       <c r="F18" t="n">
-        <v>2271341259.300789</v>
+        <v>2276525387.464984</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2271341259.300789</v>
+        <v>2276525387.464984</v>
       </c>
     </row>
     <row r="19">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4608249797.671778</v>
+        <v>4606761148.878797</v>
       </c>
       <c r="E19" t="n">
-        <v>872645836.627254</v>
+        <v>880638321.6349101</v>
       </c>
       <c r="F19" t="n">
-        <v>5480895634.299032</v>
+        <v>5487399470.513707</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5480895634.299032</v>
+        <v>5487399470.513707</v>
       </c>
     </row>
     <row r="20">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3431022674.68616</v>
+        <v>-3163578369.50797</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-3431022674.68616</v>
+        <v>-3163578369.50797</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-3431022674.68616</v>
+        <v>-3163578369.50797</v>
       </c>
     </row>
     <row r="21">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1759613838.779673</v>
+        <v>-2053697999.471197</v>
       </c>
       <c r="E21" t="n">
-        <v>-15483841.00286351</v>
+        <v>-18094369.43883081</v>
       </c>
       <c r="F21" t="n">
-        <v>-1775097679.782537</v>
+        <v>-2071792368.910028</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-1775097679.782537</v>
+        <v>-2071792368.910028</v>
       </c>
     </row>
     <row r="22">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1702312063.613388</v>
+        <v>-1702401080.108813</v>
       </c>
       <c r="E22" t="n">
-        <v>-59764962.08873813</v>
+        <v>-59578771.33794476</v>
       </c>
       <c r="F22" t="n">
-        <v>-1762077025.702126</v>
+        <v>-1761979851.446758</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>-1762077025.702126</v>
+        <v>-1761979851.446758</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1310247452.871499</v>
+        <v>1457453045.246347</v>
       </c>
       <c r="E23" t="n">
-        <v>209474717.2358064</v>
+        <v>194099408.3421885</v>
       </c>
       <c r="F23" t="n">
-        <v>1519722170.107305</v>
+        <v>1651552453.588536</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1519722170.107305</v>
+        <v>1651552453.588536</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-35646133.80847277</v>
+        <v>-101372893.4876673</v>
       </c>
       <c r="E24" t="n">
-        <v>-32583946.50832415</v>
+        <v>1439158.592390906</v>
       </c>
       <c r="F24" t="n">
-        <v>-68230080.31679693</v>
+        <v>-99933734.89527634</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>-68230080.31679693</v>
+        <v>-99933734.89527634</v>
       </c>
     </row>
     <row r="25">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>50949246.19788411</v>
+        <v>66251088.34777329</v>
       </c>
       <c r="F25" t="n">
-        <v>50949246.19788411</v>
+        <v>66251088.34777329</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>50949246.19788411</v>
+        <v>66251088.34777329</v>
       </c>
     </row>
     <row r="26">
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-55240771.49147542</v>
+        <v>-69468691.71158063</v>
       </c>
       <c r="F26" t="n">
-        <v>-55240771.49147542</v>
+        <v>-69468691.71158063</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-55240771.49147542</v>
+        <v>-69468691.71158063</v>
       </c>
     </row>
     <row r="27">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1629207873.275736</v>
+        <v>1628860571.612235</v>
       </c>
       <c r="E27" t="n">
-        <v>441838934.0193523</v>
+        <v>445725027.5769216</v>
       </c>
       <c r="F27" t="n">
-        <v>2071046807.295089</v>
+        <v>2074585599.189157</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2071046807.295089</v>
+        <v>2074585599.189157</v>
       </c>
     </row>
     <row r="28">
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4079964199.723892</v>
+        <v>4071711881.850679</v>
       </c>
       <c r="E28" t="n">
-        <v>1339021267.737889</v>
+        <v>1352178119.099703</v>
       </c>
       <c r="F28" t="n">
-        <v>5418985467.461781</v>
+        <v>5423890000.950382</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5418985467.461781</v>
+        <v>5423890000.950382</v>
       </c>
     </row>
     <row r="29">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-3570626119.017644</v>
+        <v>-3290858979.57491</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-3570626119.017644</v>
+        <v>-3290858979.57491</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-3570626119.017644</v>
+        <v>-3290858979.57491</v>
       </c>
     </row>
     <row r="30">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1746459477.633495</v>
+        <v>-2038355634.020296</v>
       </c>
       <c r="E30" t="n">
-        <v>-15342428.22534983</v>
+        <v>-17928960.69357857</v>
       </c>
       <c r="F30" t="n">
-        <v>-1761801905.858845</v>
+        <v>-2056284594.713874</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-1761801905.858845</v>
+        <v>-2056284594.713874</v>
       </c>
     </row>
     <row r="31">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-1728154165.056717</v>
+        <v>-1728462510.163216</v>
       </c>
       <c r="E31" t="n">
-        <v>-43890063.38454545</v>
+        <v>-43704205.07269439</v>
       </c>
       <c r="F31" t="n">
-        <v>-1772044228.441262</v>
+        <v>-1772166715.23591</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1772044228.441262</v>
+        <v>-1772166715.23591</v>
       </c>
     </row>
     <row r="32">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1387666416.822766</v>
+        <v>1523431444.032598</v>
       </c>
       <c r="E32" t="n">
-        <v>215993235.0308178</v>
+        <v>199851523.0777168</v>
       </c>
       <c r="F32" t="n">
-        <v>1603659651.853584</v>
+        <v>1723282967.110315</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1603659651.853584</v>
+        <v>1723282967.110315</v>
       </c>
     </row>
     <row r="33">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-52851220.97648965</v>
+        <v>-99021693.55790579</v>
       </c>
       <c r="E33" t="n">
-        <v>-14126926.9717582</v>
+        <v>1695641.78685534</v>
       </c>
       <c r="F33" t="n">
-        <v>-66978147.94824776</v>
+        <v>-97326051.77105051</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>-66978147.94824776</v>
+        <v>-97326051.77105051</v>
       </c>
     </row>
     <row r="34">
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>51918672.77361196</v>
+        <v>67393132.73991197</v>
       </c>
       <c r="F34" t="n">
-        <v>51918672.77361196</v>
+        <v>67393132.73991197</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>51918672.77361196</v>
+        <v>67393132.73991197</v>
       </c>
     </row>
     <row r="35">
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-33793464.28046042</v>
+        <v>-42637149.06883709</v>
       </c>
       <c r="F35" t="n">
-        <v>-33793464.28046042</v>
+        <v>-42637149.06883709</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-33793464.28046042</v>
+        <v>-42637149.06883709</v>
       </c>
     </row>
     <row r="36">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1717870607.287968</v>
+        <v>1718343256.140721</v>
       </c>
       <c r="E36" t="n">
-        <v>456617144.5540742</v>
+        <v>460721352.7227771</v>
       </c>
       <c r="F36" t="n">
-        <v>2174487751.842042</v>
+        <v>2179064608.863498</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2174487751.842042</v>
+        <v>2179064608.863498</v>
       </c>
     </row>
     <row r="37">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4370186303.292678</v>
+        <v>4366802186.573316</v>
       </c>
       <c r="E37" t="n">
-        <v>1043231633.793297</v>
+        <v>1052632175.58457</v>
       </c>
       <c r="F37" t="n">
-        <v>5413417937.085975</v>
+        <v>5419434362.157887</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5413417937.085975</v>
+        <v>5419434362.157887</v>
       </c>
     </row>
     <row r="38">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-3493089952.872704</v>
+        <v>-3220163562.207465</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-3493089952.872704</v>
+        <v>-3220163562.207465</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-3493089952.872704</v>
+        <v>-3220163562.207465</v>
       </c>
     </row>
     <row r="39">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1742776623.671723</v>
+        <v>-2034050387.233595</v>
       </c>
       <c r="E39" t="n">
-        <v>-15298901.92016511</v>
+        <v>-17877919.20253081</v>
       </c>
       <c r="F39" t="n">
-        <v>-1758075525.591888</v>
+        <v>-2051928306.436126</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-1758075525.591888</v>
+        <v>-2051928306.436126</v>
       </c>
     </row>
     <row r="40">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1706754645.599518</v>
+        <v>-1707099081.381651</v>
       </c>
       <c r="E40" t="n">
-        <v>-56661569.98618495</v>
+        <v>-56475765.69129982</v>
       </c>
       <c r="F40" t="n">
-        <v>-1763416215.585703</v>
+        <v>-1763574847.07295</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>-1763416215.585703</v>
+        <v>-1763574847.07295</v>
       </c>
     </row>
     <row r="41">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1346232393.261463</v>
+        <v>1484934177.228416</v>
       </c>
       <c r="E41" t="n">
-        <v>211501179.4371307</v>
+        <v>195828491.1105312</v>
       </c>
       <c r="F41" t="n">
-        <v>1557733572.698594</v>
+        <v>1680762668.338947</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1557733572.698594</v>
+        <v>1680762668.338947</v>
       </c>
     </row>
     <row r="42">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-45921221.17908719</v>
+        <v>-99156529.54694462</v>
       </c>
       <c r="E42" t="n">
-        <v>-20112574.33891214</v>
+        <v>3080084.276922567</v>
       </c>
       <c r="F42" t="n">
-        <v>-66033795.5179993</v>
+        <v>-96076445.27002198</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-66033795.5179993</v>
+        <v>-96076445.27002198</v>
       </c>
     </row>
     <row r="43">
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>51047586.25519484</v>
+        <v>66319645.12209173</v>
       </c>
       <c r="F43" t="n">
-        <v>51047586.25519484</v>
+        <v>66319645.12209173</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>51047586.25519484</v>
+        <v>66319645.12209173</v>
       </c>
     </row>
     <row r="44">
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-43707800.03966388</v>
+        <v>-54998302.34552281</v>
       </c>
       <c r="F44" t="n">
-        <v>-43707800.03966388</v>
+        <v>-54998302.34552281</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-43707800.03966388</v>
+        <v>-54998302.34552281</v>
       </c>
     </row>
     <row r="45">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1667080655.739377</v>
+        <v>1667202507.097859</v>
       </c>
       <c r="E45" t="n">
-        <v>446722472.4544179</v>
+        <v>450701814.6050242</v>
       </c>
       <c r="F45" t="n">
-        <v>2113803128.193795</v>
+        <v>2117904321.702883</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2113803128.193795</v>
+        <v>2117904321.702883</v>
       </c>
     </row>
     <row r="46">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4212433738.29099</v>
+        <v>4207158136.440301</v>
       </c>
       <c r="E46" t="n">
-        <v>1177744043.618858</v>
+        <v>1188583752.960017</v>
       </c>
       <c r="F46" t="n">
-        <v>5390177781.909848</v>
+        <v>5395741889.400318</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5390177781.909848</v>
+        <v>5395741889.400318</v>
       </c>
     </row>
     <row r="47">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3521631895.511834</v>
+        <v>-3246193787.08432</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-3521631895.511834</v>
+        <v>-3246193787.08432</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-3521631895.511834</v>
+        <v>-3246193787.08432</v>
       </c>
     </row>
     <row r="48">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1765338338.610486</v>
+        <v>-2060387996.826856</v>
       </c>
       <c r="E48" t="n">
-        <v>-15550741.29227038</v>
+        <v>-18172797.48107013</v>
       </c>
       <c r="F48" t="n">
-        <v>-1780889079.902756</v>
+        <v>-2078560794.307926</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>-1780889079.902756</v>
+        <v>-2078560794.307926</v>
       </c>
     </row>
     <row r="49">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1728920322.026629</v>
+        <v>-1728948425.629918</v>
       </c>
       <c r="E49" t="n">
-        <v>-43910420.05504028</v>
+        <v>-43724138.14290109</v>
       </c>
       <c r="F49" t="n">
-        <v>-1772830742.08167</v>
+        <v>-1772672563.772819</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1772830742.08167</v>
+        <v>-1772672563.772819</v>
       </c>
     </row>
     <row r="50">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1358832326.732567</v>
+        <v>1502910844.795021</v>
       </c>
       <c r="E50" t="n">
-        <v>214935859.3762352</v>
+        <v>198985314.0901184</v>
       </c>
       <c r="F50" t="n">
-        <v>1573768186.108802</v>
+        <v>1701896158.885139</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1573768186.108802</v>
+        <v>1701896158.885139</v>
       </c>
     </row>
     <row r="51">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-43167099.5280119</v>
+        <v>-101471922.7516716</v>
       </c>
       <c r="E51" t="n">
-        <v>-26414108.66164763</v>
+        <v>-302563.3581481716</v>
       </c>
       <c r="F51" t="n">
-        <v>-69581208.18965958</v>
+        <v>-101774486.1098198</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>-69581208.18965958</v>
+        <v>-101774486.1098198</v>
       </c>
     </row>
     <row r="52">
@@ -2358,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>52041402.59864988</v>
+        <v>67601240.99383162</v>
       </c>
       <c r="F52" t="n">
-        <v>52041402.59864988</v>
+        <v>67601240.99383162</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>52041402.59864988</v>
+        <v>67601240.99383162</v>
       </c>
     </row>
     <row r="53">
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>-43588973.21809262</v>
+        <v>-54926816.28068642</v>
       </c>
       <c r="F53" t="n">
-        <v>-43588973.21809262</v>
+        <v>-54926816.28068642</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-43588973.21809262</v>
+        <v>-54926816.28068642</v>
       </c>
     </row>
     <row r="54">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1688842744.04984</v>
+        <v>1688874333.3194</v>
       </c>
       <c r="E54" t="n">
-        <v>453763954.7393798</v>
+        <v>457796793.9536396</v>
       </c>
       <c r="F54" t="n">
-        <v>2142606698.789219</v>
+        <v>2146671127.27304</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2142606698.789219</v>
+        <v>2146671127.27304</v>
       </c>
     </row>
     <row r="55">
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4261447978.416411</v>
+        <v>4255276940.553149</v>
       </c>
       <c r="E55" t="n">
-        <v>1187583015.60945</v>
+        <v>1199159578.170372</v>
       </c>
       <c r="F55" t="n">
-        <v>5449030994.025861</v>
+        <v>5454436518.72352</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5449030994.025861</v>
+        <v>5454436518.72352</v>
       </c>
     </row>
     <row r="56">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-3577843923.188877</v>
+        <v>-3297443579.731035</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-3577843923.188877</v>
+        <v>-3297443579.731035</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>-3577843923.188877</v>
+        <v>-3297443579.731035</v>
       </c>
     </row>
     <row r="57">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1758534376.095333</v>
+        <v>-2052450718.820964</v>
       </c>
       <c r="E57" t="n">
-        <v>-15476937.61869058</v>
+        <v>-18086449.29324332</v>
       </c>
       <c r="F57" t="n">
-        <v>-1774011313.714024</v>
+        <v>-2070537168.114208</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>-1774011313.714024</v>
+        <v>-2070537168.114208</v>
       </c>
     </row>
     <row r="58">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1738145377.778625</v>
+        <v>-1738282605.209455</v>
       </c>
       <c r="E58" t="n">
-        <v>-38192330.92807065</v>
+        <v>-38006214.05604113</v>
       </c>
       <c r="F58" t="n">
-        <v>-1776337708.706696</v>
+        <v>-1776288819.265496</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>-1776337708.706696</v>
+        <v>-1776288819.265496</v>
       </c>
     </row>
     <row r="59">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1390090199.843369</v>
+        <v>1529139314.539308</v>
       </c>
       <c r="E59" t="n">
-        <v>217409195.1515212</v>
+        <v>201162732.3125564</v>
       </c>
       <c r="F59" t="n">
-        <v>1607499394.994891</v>
+        <v>1730302046.851864</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1607499394.994891</v>
+        <v>1730302046.851864</v>
       </c>
     </row>
     <row r="60">
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-50514098.88786048</v>
+        <v>-100329434.023942</v>
       </c>
       <c r="E60" t="n">
-        <v>-18323108.1958431</v>
+        <v>-11546.42158665182</v>
       </c>
       <c r="F60" t="n">
-        <v>-68837207.08370358</v>
+        <v>-100340980.4455287</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>-68837207.08370358</v>
+        <v>-100340980.4455287</v>
       </c>
     </row>
     <row r="61">
@@ -2664,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>52376409.34303474</v>
+        <v>67988799.27875632</v>
       </c>
       <c r="F61" t="n">
-        <v>52376409.34303474</v>
+        <v>67988799.27875632</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>52376409.34303474</v>
+        <v>67988799.27875632</v>
       </c>
     </row>
     <row r="62">
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-34779061.88385776</v>
+        <v>-43904630.89688604</v>
       </c>
       <c r="F62" t="n">
-        <v>-34779061.88385776</v>
+        <v>-43904630.89688604</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>-34779061.88385776</v>
+        <v>-43904630.89688604</v>
       </c>
     </row>
     <row r="63">
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1724311624.301515</v>
+        <v>1724693775.493838</v>
       </c>
       <c r="E63" t="n">
-        <v>459437379.7355413</v>
+        <v>463557439.3799594</v>
       </c>
       <c r="F63" t="n">
-        <v>2183749004.037056</v>
+        <v>2188251214.873798</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2183749004.037056</v>
+        <v>2188251214.873798</v>
       </c>
     </row>
     <row r="64">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4379700742.660229</v>
+        <v>4375607649.124945</v>
       </c>
       <c r="E64" t="n">
-        <v>1063636123.353978</v>
+        <v>1073606448.916451</v>
       </c>
       <c r="F64" t="n">
-        <v>5443336866.014207</v>
+        <v>5449214098.041395</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5443336866.014207</v>
+        <v>5449214098.041395</v>
       </c>
     </row>
   </sheetData>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-42119080.78378276</v>
+        <v>-6035350.758562114</v>
       </c>
       <c r="C2" t="n">
-        <v>1941323300.337283</v>
+        <v>1979071700.688118</v>
       </c>
       <c r="D2" t="n">
-        <v>1899204219.5535</v>
+        <v>1973036349.929555</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-109259092.8678579</v>
+        <v>-121961996.8212447</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.104924405654828</v>
+        <v>-10.16349973510373</v>
       </c>
       <c r="H2" t="n">
-        <v>-109259092.8678579</v>
+        <v>-121961996.8212447</v>
       </c>
       <c r="I2" t="n">
-        <v>-9.104924405654828</v>
+        <v>-10.16349973510373</v>
       </c>
     </row>
     <row r="3">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>570592684.6089693</v>
+        <v>660434595.3802178</v>
       </c>
       <c r="C3" t="n">
-        <v>1557753565.290091</v>
+        <v>1568881944.605393</v>
       </c>
       <c r="D3" t="n">
-        <v>2128346249.89906</v>
+        <v>2229316539.985611</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>119882937.4777024</v>
+        <v>134318193.2348108</v>
       </c>
       <c r="G3" t="n">
-        <v>9.990244789808532</v>
+        <v>11.19318276956757</v>
       </c>
       <c r="H3" t="n">
-        <v>59941468.73885119</v>
+        <v>67159096.61740541</v>
       </c>
       <c r="I3" t="n">
-        <v>4.995122394904266</v>
+        <v>5.596591384783784</v>
       </c>
     </row>
     <row r="4">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90824814.98343299</v>
+        <v>136975156.1336146</v>
       </c>
       <c r="C4" t="n">
-        <v>1878210644.09953</v>
+        <v>1912550969.470621</v>
       </c>
       <c r="D4" t="n">
-        <v>1969035459.082963</v>
+        <v>2049526125.604236</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-39427853.33839488</v>
+        <v>-45472221.14656448</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.28565444486624</v>
+        <v>-3.789351762213707</v>
       </c>
       <c r="H4" t="n">
-        <v>-39427853.33839488</v>
+        <v>-45472221.14656448</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.28565444486624</v>
+        <v>-3.789351762213707</v>
       </c>
     </row>
     <row r="5">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>377632344.7190661</v>
+        <v>451878069.4303069</v>
       </c>
       <c r="C5" t="n">
-        <v>1660607803.289687</v>
+        <v>1678023511.076722</v>
       </c>
       <c r="D5" t="n">
-        <v>2038240148.008754</v>
+        <v>2129901580.507029</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29776835.58739567</v>
+        <v>34903233.75622845</v>
       </c>
       <c r="G5" t="n">
-        <v>2.481402965616306</v>
+        <v>2.908602813019037</v>
       </c>
       <c r="H5" t="n">
-        <v>14888417.79369783</v>
+        <v>17451616.87811422</v>
       </c>
       <c r="I5" t="n">
-        <v>1.240701482808153</v>
+        <v>1.454301406509519</v>
       </c>
     </row>
     <row r="6">
@@ -2980,13 +2980,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>237204343.9687985</v>
+        <v>298825260.3969212</v>
       </c>
       <c r="C6" t="n">
-        <v>1751234435.480675</v>
+        <v>1775161800.835233</v>
       </c>
       <c r="D6" t="n">
-        <v>1988438779.449474</v>
+        <v>2073987061.232154</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2994,16 +2994,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-20024532.97188425</v>
+        <v>-21011285.518646</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.668711080990354</v>
+        <v>-1.750940459887167</v>
       </c>
       <c r="H6" t="n">
-        <v>-20024532.97188425</v>
+        <v>-21011285.518646</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.668711080990354</v>
+        <v>-1.750940459887167</v>
       </c>
     </row>
     <row r="7">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250065393.5218567</v>
+        <v>310059986.3748043</v>
       </c>
       <c r="C7" t="n">
-        <v>1778859989.096664</v>
+        <v>1806416611.945156</v>
       </c>
       <c r="D7" t="n">
-        <v>2028925382.61852</v>
+        <v>2116476598.31996</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3027,16 +3027,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20462070.19716263</v>
+        <v>21478251.56916022</v>
       </c>
       <c r="G7" t="n">
-        <v>1.705172516430219</v>
+        <v>1.789854297430018</v>
       </c>
       <c r="H7" t="n">
-        <v>10231035.09858131</v>
+        <v>10739125.78458011</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8525862582151095</v>
+        <v>0.8949271487150092</v>
       </c>
     </row>
     <row r="8">
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>369064790.8544175</v>
+        <v>440934401.3726938</v>
       </c>
       <c r="C8" t="n">
-        <v>1686087668.957613</v>
+        <v>1706306579.219966</v>
       </c>
       <c r="D8" t="n">
-        <v>2055152459.812031</v>
+        <v>2147240980.59266</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>46689147.39067268</v>
+        <v>52242633.84185982</v>
       </c>
       <c r="G8" t="n">
-        <v>3.890762282556057</v>
+        <v>4.353552820154985</v>
       </c>
       <c r="H8" t="n">
-        <v>23344573.69533634</v>
+        <v>26121316.92092991</v>
       </c>
       <c r="I8" t="n">
-        <v>1.945381141278028</v>
+        <v>2.176776410077493</v>
       </c>
     </row>
   </sheetData>
